--- a/data/papers_filtrados.xlsx
+++ b/data/papers_filtrados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,20 +511,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CARE-AD: a multi-agent large language model framework for Alzheimer’s disease prediction using longitudinal clinical notes</t>
+          <t>INTELLIGENT TRAFFIC MANAGEMENT SYSTEM FOR A MINING ENTERPRISE BASED ON A MULTI-AGENT APPROACH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rumeng Li; Xun Wang; Dan Berlowitz; J. Mez; Honghuang Lin; Hong Yu</t>
+          <t>Yevhenii Koroviaka; V. Khomenko; O. Pashchenko; S. Shevchenko; O. Dreshpak</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>npj Digital Medicine</t>
+          <t>Naukovyi visnyk Donetskoho natsionalnoho tekhnichnoho universytetu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,12 +534,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.1038/s41746-025-01940-4</t>
+          <t>10.31474/2415-7902-2026-2-17-6-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Large language models (LLMs) have shown promising capabilities across diverse domains, yet their application to complex clinical prediction tasks remains limited. In this study, we present CARE-AD (Collaborative Analysis and Risk Evaluation for Alzheimer’s Disease), a multi-agent LLM-based framework for forecasting Alzheimer’s disease (AD) onset by analyzing longitudinal electronic health record (EHR) notes. CARE-AD assigns specialized LLM agents to extract signs and symptoms relevant to AD and conduct domain-specific evaluations—emulating a collaborative diagnostic process. In a retrospective evaluation, CARE-AD achieved higher accuracy (0.53 vs. 0.26–0.45) than baseline single-model approaches in predicting AD risk 10 years prior to the first recorded diagnosis code. These findings highlight the feasibility of using multi-agent LLM systems to support early risk assessment for AD and motivate further research on their integration into clinical decision support workflows.</t>
+          <t>Objective. To develop, formalize, and evaluate a decentralized multi-agent system for real‑time traffic management in autonomous open‑pit mining operations, aimed at minimizing truck idle time, preventing congestion and deadlocks, and increasing overall haulage efficiency.
+Methodology. The system is designed using a multi‑agent paradigm where haul trucks, excavators,dumping points, and key infrastructure elements are modeled as autonomous agents. Task allocation is performed via a market‑based Contract Net Protocol with bidding based on estimated time of arrival. Path planning employs an A* algorithm on a dynamic graph, while conflict resolution is achieved through a reservation mechanism managed by infrastructure agents. Reinforcement learning (Q‑learning) is integrated to allow truck agents to
+adapt their bidding strategies over time. The approach is validated through agent‑based simulations under normal, high‑intensity, and disruption scenarios, and compared against a centralized first‑come, first‑served dispatch system.
+Results. Under normal operation, the multi‑agent system reduced average truck idle time by 44%, cycle time by 17.5%, increased throughput by 21%, and lowered traffic conflict frequency by 66.5% compared to the baseline. In high‑intensity traffic, it prevented congestion and deadlocks, maintaining smooth flow. During unexpected disruptions (excavator breakdown, road blockage), the system autonomously re‑planned routes and reassigned tasks within minutes, effectively isolating the impact and ensuring operational continuity.
+Scientific novelty. The novelty lies in the holistic integration of decentralized coordination, market‑based task allocation, dynamic path reservation, and reinforcement learning within a unified multi‑agent framework for real‑time traffic management in open‑pit mining. This approach enables emergent self‑organization, robust adaptation to dynamic conditions, and scalability beyond the capabilities of traditional centralized fleet management systems.
+Practical significance. The proposed system offers a scalable and resilient solution for autonomous haulage fleets, directly reducing operational costs through lower idle times and higher throughput, improving safety by preventing traffic conflicts, and enhancing resilience to equipment failures or route blockages. It provides a clear pathway for transitioning existing mines to fully autonomous, efficient, and safe operations.
+Keywords: multi-agent system, traffic management, open-pit mining, autonomous haulage, fleet management, reinforcement learning, Contract Net Protocol, path planning, conflict resolution, simulation.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,21 +563,21 @@
         <v>1</v>
       </c>
       <c r="L2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -580,19 +586,19 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DruGagent: Multi-Agent Large Language Model-Based Reasoning for Drug-Target Interaction Prediction</t>
+          <t>Distributed multi-agent reinforcement learning for multi-objective optimal dispatch of microgrids.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yoshitaka Inoue; Tianci Song; Xinlin Wang; Augustin Luna; Tianfan Fu</t>
+          <t>Xiaowen Wang; Shuai Liu; Qian-Wen Xu; Xin-Quan Shao</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -600,7 +606,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>ISA transactions</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,10 +614,14 @@
           <t>journal</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.1016/j.isatra.2025.01.009</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Advancements in large language models (LLMs) allow them to address diverse questions using human-like interfaces. Still, limitations in their training prevent them from answering accurately in scenarios that could benefit from multiple perspectives. Multi-agent systems allow the resolution of questions to enhance result consistency and reliability. While drug-target interaction (DTI) prediction is important for drug discovery, existing approaches face challenges due to complex biological systems and the lack of interpretability needed for clinical applications. DrugAgent is a multi-agent LLM system for DTI prediction that combines multiple specialized perspectives with transparent reasoning. Our system adapts and extends existing multi-agent frameworks by (1) applying coordinator-based architecture to the DTI domain, (2) integrating domain-specific data sources, including ML predictions, knowledge graphs, and literature evidence, and (3) incorporating Chain-of-Thought (CoT) and ReAct (Reason+Act) frameworks for transparent DTI reasoning. We conducted comprehensive experiments using a kinase inhibitor dataset, where our multi-agent LLM method outperformed the non-reasoning multi-agent model (GPT-4o mini) by 45% in F1 score (0.514 vs 0.355). Through ablation studies, we demonstrated the contributions of each agent, with the AI agent being the most impactful, followed by the KG agent and search agent. Most importantly, our approach provides detailed, human-interpretable reasoning for each prediction by combining evidence from multiple sources - a critical feature for biomedical applications where understanding the rationale behind predictions is essential for clinical decision-making and regulatory compliance. Code is available at https://anonymous.4open.science/r/DrugAgent-B2EA.</t>
+          <t>The distributed microgrids cooperate to accomplish economic and environmental objectives, which have a vital impact on maintaining the reliable and economic operation of power systems. Therefore a distributed multi-agent reinforcement learning (MARL) algorithm is put forward incorporating the actor-critic architecture, which learns multiple critics for subtasks and utilizes only information from neighbors to find dispatch strategy. Based on our proposed algorithm, multi-objective optimal dispatch problem of microgrids with continuous state changes and power values is dealt with. Meanwhile, the computation and communication resources requirements are greatly reduced and the privacy of each agent is protected in the process of information interaction. In addition, the convergence for the proposed algorithm is guaranteed with the adoption of linear function approximation. Simulation results validate the performance of the algorithm, demonstrating its effectiveness in achieving multi-objective optimal dispatch in microgrids.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -629,17 +639,17 @@
         <v>1</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -652,19 +662,19 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Multi-Agent Large Language Model Frameworks: Unlocking New Possibilities for Optimizing Wastewater Treatment Operation.</t>
+          <t>Economic Load Dispatch of A Multi‐Area Power System Using Multi‐Agent Distributed Optimization Based on Genetic Algorithm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samuel Rothfarb; Mikayla Friday; Xingyu Wang; Arash Zaghi; Bai-Kun Li</t>
+          <t>Seyed Yaser Fakhrmousavi; Seyed Babak Mazafari; S. Javadi; M. Aliabadi</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -672,7 +682,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Environmental Research</t>
+          <t>Energy Science &amp;amp; Engineering</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -682,12 +692,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.1016/j.envres.2025.121401</t>
+          <t>10.1002/ese3.2086</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Wastewater treatment plants (WWTPs) are highly complex systems where biological, chemical, and physical processes interact dynamically, creating significant operational challenges. Traditional modeling approaches, such as Activated Sludge Models (ASMs) and machine learning algorithms (MLAs), struggle to process the unstructured and multimodal data generated in WWTPs, limiting their effectiveness. Large Language Models (LLMs) offer a promising solution by integrating diverse data sources, recognizing patterns, and enabling human-in-the-loop interactions for informed decision-making. However, the complexity of WWTP operations exceeds the capabilities of a single LLM, necessitating a multi-agent framework where specialized agents collaborate to analyze diverse data streams and generate targeted recommendations. This perspective paper highlights how multi-agent, tool-equipped LLMs can enhance process control, optimize decision-making, and improve real-time adaptability in WWTPs. A case study on sludge bulking illustrates their potential over traditional methods. While challenges such as computational costs and AI-driven decision risks exist, they can be mitigated through validation, human oversight, and interpretability tools. Multi-agent LLMs represent a scalable and adaptable approach, positioning AI-driven decision support as a key innovation for WWTP operations.</t>
+          <t>This study presents a new methodology for distributed multi‐agent optimization utilizing a genetic algorithm to address Multi‐Area Economic Dispatch Problem (MAEDP) in a power system. While numerous studies have been conducted on various optimization methods for distributed multi‐agent systems, this paper proposes a model for solving the optimal economic dispatch equations in different areas of the power system in a distributed and coordinated manner. In this model, each area is represented by an agent responsible for coordinating data exchange with other areas and solving the generation dispatch equations within its own area. The coordination model between agents and areas is described in the form of an algorithm, whereby the exchanged data values converge after several iterations, and the final solution to the problem is obtained from the perspective of each agent. The objective of each agent in each area is to minimize generation costs and meet its own area's load demand while maintaining voltage profiles. Each agent sets the power generation values of resources in each area using the genetic algorithm rules and then solves the distributed power flow equations using the proposed method. Upon achieving convergence, each agent evaluates all operational constraints within its designated region, calculates the associated generation cost, and shares the cost value to other agents, thereby facilitating the computation of the total cost for each agent. This process continues until the best possible solution is found. The results of implementing the proposed model and algorithm on several different test networks of power systems demonstrate the capability and effectiveness of the method in decomposing the optimal economic dispatch problem into smaller sub‐problems and then finding the final optimal solution through simultaneous solving with agent consensus in coordinated steps.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -705,17 +715,17 @@
         <v>1</v>
       </c>
       <c r="L4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -728,27 +738,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multi-agent large language model framework for code-compliant automated design of reinforced concrete structures</t>
+          <t>MACM: Utilizing a Multi-Agent System for Condition Mining in Solving Complex Mathematical Problems</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jinxin Chen; Yi Bao</t>
+          <t>Bin Lei; Yi Zhang; Shan Zuo; Ali Payani; Cai-Wen Ding</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Automation in Construction</t>
+          <t>Neural Information Processing Systems</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -758,10 +768,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.1016/j.autcon.2025.106331</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>10.48550/arXiv.2404.04735</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Recent advancements in large language models, such as GPT-4, have demonstrated remarkable capabilities in processing standard queries. Despite these advancements, their performance substantially declines in \textbf{advanced mathematical problems requiring complex, multi-step logical reasoning}. To enhance their inferential capabilities, current research has delved into \textit{prompting engineering}, exemplified by methodologies such as the Tree of Thought and Graph of Thought. Nonetheless, these existing approaches encounter two significant limitations. Firstly, their effectiveness in tackling complex mathematical problems is somewhat constrained. Secondly, the necessity to design distinct prompts for individual problems hampers their generalizability. In response to these limitations, this paper introduces the \textit{Multi-Agent System for conditional Mining} (\textbf{MACM}) prompting method. It not only resolves intricate mathematical problems but also demonstrates strong generalization capabilities across various mathematical contexts. With the assistance of MACM, the accuracy of GPT-4 Turbo on the most challenging level five mathematical problems in the MATH dataset increase from $\mathbf{54.68\%} \text{ to } \mathbf{76.73\%}$. The code is available in \url{https://github.com/bin123apple/MACM}.</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -800,19 +814,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CASSIA: a multi-agent large language model for automated and interpretable cell annotation</t>
+          <t>Intelligent Scheduling in Open-Pit Mining: A Multi-Agent System with Reinforcement Learning</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Elliot Xie; Ling-Xin Cheng; Jack M. Shireman; Yujia Cai; Jihua Liu; Chitrasen Mohanty; Mahua Dey; C. Kendziorski</t>
+          <t>Gabriel Icarte-Ahumada; O. Herzog</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -820,7 +834,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nature Communications</t>
+          <t>Machines</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -830,12 +844,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.1038/s41467-025-67084-x</t>
+          <t>10.3390/machines13050350</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cell type annotation is an essential step in single-cell RNA-sequencing analysis, and numerous annotation methods are available. Most require a combination of computational and domain-specific expertise, and they frequently yield inconsistent results that can be challenging to interpret. Large language models have the potential to expand accessibility while reducing manual input and improving accuracy, but existing approaches suffer from hyperconfidence, hallucinations, and lack of reasoning. To address these limitations, we developed CASSIA for automated, accurate, and interpretable cell annotation of single-cell RNA-sequencing data. As demonstrated in analyses of 970 cell types, CASSIA improves annotation accuracy in benchmark datasets as well as complex and rare cell populations, and also provides users with reasoning and quality assessment to ensure interpretability, guard against hallucinations, and calibrate confidence. Assigning cell types in single-cell RNA-seq is essential yet challenging, as it requires expertise, time, and is often subjective. Here, the authors present CASSIA, a multi-agent AI system that provides automated, interpretable, and quality-controlled annotations with high accuracy.</t>
+          <t>An important process in the mining industry is material handling, where trucks are responsible for transporting materials extracted by shovels to different locations within the mine. The decision about the destination of a truck is very important to ensure an efficient material handling operation. Currently, this decision-making process is managed by centralized systems that apply dispatching criteria. However, this approach has the disadvantage of not providing accurate dispatching solutions due to the lack of awareness of potentially changing external conditions and the reliance on a central node. To address this issue, we previously developed a multi-agent system for truck dispatching (MAS-TD), where intelligent agents representing real-world equipment collaborate to generate schedules. Recently, we extended the MAS-TD (now MAS-TDRL) by incorporating learning capabilities and compared its performance with the original MAS-TD, which lacks learning capabilities. This comparison was made using simulated scenarios based on actual data from a Chilean open-pit mine. The results show that the MAS-TDRL generates more efficient schedules.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -853,21 +867,21 @@
         <v>1</v>
       </c>
       <c r="L6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -876,19 +890,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LLM-Agent-Controller: A Universal Multi-Agent Large Language Model System as a Control Engineer</t>
+          <t>Symmetric Policy Design for Multi-Agent Dispatch Coordination in Supply Chains</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rasoul Zahedifar; Sayyed Ali Mirghasemi; M. Baghshah; Alireza Taheri</t>
+          <t>Sagar Sudhakara</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -906,12 +920,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2505.19567</t>
+          <t>10.48550/arXiv.2504.19397</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>This study presents the LLM-Agent-Controller, a multi-agent large language model (LLM) system developed to address a wide range of problems in control engineering (Control Theory). The system integrates a central controller agent with multiple specialized auxiliary agents, responsible for tasks such as controller design, model representation, control analysis, time-domain response, and simulation. A supervisor oversees high-level decision-making and workflow coordination, enhancing the system's reliability and efficiency. The LLM-Agent-Controller incorporates advanced capabilities, including Retrieval-Augmented Generation (RAG), Chain-of-Thought reasoning, self-criticism and correction, efficient memory handling, and user-friendly natural language communication. It is designed to function without requiring users to have prior knowledge of Control Theory, enabling them to input problems in plain language and receive complete, real-time solutions. To evaluate the system, we propose new performance metrics assessing both individual agents and the system as a whole. We test five categories of Control Theory problems and benchmark performance across three advanced LLMs. Additionally, we conduct a comprehensive qualitative conversational analysis covering all key services. Results show that the LLM-Agent-Controller successfully solved 83% of general tasks, with individual agents achieving an average success rate of 87%. Performance improved with more advanced LLMs. This research demonstrates the potential of multi-agent LLM architectures to solve complex, domain-specific problems. By integrating specialized agents, supervisory control, and advanced reasoning, the LLM-Agent-Controller offers a scalable, robust, and accessible solution framework that can be extended to various technical domains.</t>
+          <t>We study a decentralized dispatch coordination problem in a multi-agent supply chain setting with shared logistics capacity. We propose symmetric (identical) dispatch strategies for all agents, enabling efficient coordination without centralized control. Using a common information approach, we derive a dynamic programming solution that computes optimal symmetric dispatch strategies by transforming the multi-agent problem into a tractable dynamic program on the agents common information state. Simulation results demonstrate that our method significantly reduces coordination cost compared to baseline heuristics, including belief-based strategies and an always-dispatch policy. These findings highlight the benefits of combining symmetric strategy design with a common information-based dynamic programming framework for improving multi-agent coordination performance.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -929,17 +943,17 @@
         <v>1</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -952,27 +966,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ShapefileGPT: a multi-agent large language model framework for automated shapefile processing</t>
+          <t>GRAND: Guidance, Rebalancing, and Assignment for Networked Dispatch in Multi-Agent Path Finding</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qingming Lin; Rui Hu; Hua-Xia Li; Sensen Wu; Yadong Li; Kai Fang; Hai-Lin Feng; Zhenhong Du; Liu-Chang Xu</t>
+          <t>J. Gaber; Meshal Alharbi; Daniele Gammelli; Gioele Zardini</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>International Journal of Digital Earth</t>
+          <t>IEEE Robotics and Automation Letters</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -982,12 +996,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.1080/17538947.2025.2577884</t>
+          <t>10.1109/LRA.2026.3673902</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ABSTRACT Vector data is a core structure in geographic information science (GIS), with Shapefile being the industry standard format. However, processing such data requires domain expertise, obstructing interdisciplinary research in spatial data analysis. While large language models (LLMs) exhibit breakthroughs in natural language processing and task automation, they still face challenges in handling the spatial-topological complexities inherent in GIS vector data. To address these challenges, we propose ShapefileGPT, an innovative LLM-powered framework for automating Shapefile processing in spatial analysis. ShapefileGPT utilizes a multi-agent architecture comprising the planner and worker. The planner orchestrates task decomposition and supervision, while the worker implements spatial operation execution. We organized a custom spatial analysis library with API documentation, enabling the worker agent to efficiently process Shapefiles through function calls and validate the framework’s effectiveness. For evaluation, we constructed a preliminary evaluation dataset based on authoritative textbooks, encompassing tasks in categories such as geometric operations and spatial queries. ShapefileGPT achieved a 95.24% task success rate, outperforming GPT models. Compared to general-purpose LLMs, it effectively handles complex vector data analysis, demonstrating superior spatial data understanding and analytical capabilities. This innovation expands the possibilities for GIS automation, with promising implications for interdisciplinary spatial analysis and applications.</t>
+          <t>Large robot fleets are now common in warehouses and other logistics settings, where small control gains translate into large operational impacts. In this article, we address task scheduling for lifelong Multi-Agent Pickup-and-Delivery (MAPD) and propose a hybrid method that couples learning-based global guidance with lightweight optimization. A graph neural network policy trained via reinforcement learning outputs a desired distribution of free agents over an aggregated warehouse graph. This signal is converted into region-to-region rebalancing through a minimum-cost flow, and finalized by small, local assignment problems, preserving accuracy while keeping per-step latency within a 1 s compute budget. We call this approach GRAND: a hierarchical algorithm that relies on Guidance, Rebalancing, and Assignment to explicitly leverage the workspace Network structure and Dispatch agents to tasks. On congested warehouse benchmarks from the League of Robot Runners (LoRR) with up to 500 agents, our approach improves throughput by up to 10% over the 2024 winning scheduler while maintaining real-time execution. The results indicate that coupling graph-structured learned guidance with tractable solvers reduces congestion and yields a practical, scalable blueprint for high-throughput scheduling in large fleets.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1005,17 +1019,17 @@
         <v>1</v>
       </c>
       <c r="L8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1028,27 +1042,27 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Automating structural reliability analysis with a multi-agent large language model framework</t>
+          <t>Multi‐Agent Based Distributed Computing for Photovoltaic Systems Economic Dispatch Using Modified Exact Diffusion Strategy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jaehwan Jeon; Chang Hee Lee; Taeyong Kim</t>
+          <t>Wenjie Zhu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>Internet Technology Letters</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1058,12 +1072,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2607.16580</t>
+          <t>10.1002/itl2.70124</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Structural reliability analysis supports the design and safety assessment of buildings and civil infrastructure but requires specialized expertise throughout the workflow. This study presents a multi-agent large language model framework that automates component-level reliability analysis from a natural-language problem statement to interpreted estimates of the reliability index and failure probability. Specialized agents handle problem formulation, method planning, code generation, execution, and result interpretation, with human confirmation at key decision points. The Method Planner is fine-tuned using QLoRA for a priori reliability-method category selection. Analysis results are not generated directly by an LLM; instead, validated deterministic solvers compute the reliability estimates, improving reproducibility and reducing hallucination risk. The framework uses open-weight models and supports local execution without closed APIs. Results show that it lowers the expertise barrier to structural reliability assessment while preserving computational trustworthiness.</t>
+          <t>With the rapid deployment of photovoltaic (PV) systems and the transition toward decentralized energy infrastructures, traditional centralized economic dispatch methods are increasingly challenged by scalability bottlenecks, communication overhead, and vulnerability to single‐point failures. These issues are further exacerbated by the dynamic and distributed nature of PV‐based microgrids, where plug‐and‐play devices, intermittent generation, and privacy constraints demand localized decision‐making and coordination. To address these challenges, this paper proposes a fully distributed economic dispatch framework based on a multi‐agent system and a Modified Exact Diffusion Algorithm (MEDA). The framework models PV units, battery storage, flexible loads, and grid interfaces as autonomous agents that interact through peer‐to‐peer communication, collaboratively achieving global optimality without centralized supervision. A SOC‐aware battery cost model, dynamic electricity pricing, and quadratic line loss modeling are integrated to enhance practical realism. Simulation results on a modified IEEE 33‐bus microgrid show that the proposed approach significantly outperforms centralized and existing distributed methods in terms of cost reduction, convergence speed, resilience to communication failures, and adaptability to agent dynamics.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1081,17 +1095,17 @@
         <v>1</v>
       </c>
       <c r="L9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1104,27 +1118,23 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Decision Protocols in Multi-Agent Large Language Model Conversations</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Lars Benedikt Kaesberg</t>
-        </is>
-      </c>
+          <t>Optimal Distributed Dispatch of Smart Multi-Agent Energy Hubs Based on Consensus Algorithm Considering Lossy Communication Network and Uncertainty</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>CSEE Journal of Power and Energy Systems</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1134,14 +1144,10 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2607.05477</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Improving the task performance of Large Language Models (LLMs) is essential, yet scaling these models faces significant challenges such as diminishing returns and high costs. Multi-Agent Systems (MAS) offer a promising solution by distributing tasks among specialized agents to improve the overall task performance. This can reduce training costs at the expense of increased test time due to the discussion and decision-making process. The decision protocol is a critical component of MAS because it specifies how multiple agents collaborate to create a final solution. This thesis introduces the Multi-Agent LLM (MALLM) framework, which implements and evaluates various decision protocols, namely voting, consensus, and judge decision mechanisms, to simulate multi-agent discussions for conversational task solving. Unlike previous work that used a single decision protocol or tested them on limited datasets, this study systematically examines their impact on a diverse set of tasks, ranging from knowledge-based datasets (MMLU, MMLU-Pro, GPQA) and logic-based datasets (StrategyQA, MuSR, Math-lvl-5, SQuAD 2.0). The results indicate that consensus protocols excel in knowledge-intensive domains while voting and judge protocols are more effective for logic-based tasks. Increasing response diversity through independent solution generation improves decision quality, while changes in information access during the decision process have minimal impact.</t>
-        </is>
-      </c>
+          <t>10.17775/cseejpes.2023.00670</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -1157,17 +1163,17 @@
         <v>1</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1180,19 +1186,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AgentSafe: Safeguarding Large Language Model-based Multi-agent Systems via Hierarchical Data Management</t>
+          <t>Dual-layer coordination framework for urban mining: Integration of social network analysis and multi-agent systems.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Junyuan Mao; Fanci Meng; Yifan Duan; Miao Yu; X. Jia; Junfeng Fang; Yuxuan Liang; Kun Wang; Qingsong Wen</t>
+          <t>Liqiang Chen; Ming Gao; Kai-Rong Liang; Andrea Appolloni</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1200,7 +1206,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>Journal of Environmental Management</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1210,12 +1216,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2503.04392</t>
+          <t>10.1016/j.jenvman.2025.126211</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Large Language Model based multi-agent systems are revolutionizing autonomous communication and collaboration, yet they remain vulnerable to security threats like unauthorized access and data breaches. To address this, we introduce AgentSafe, a novel framework that enhances MAS security through hierarchical information management and memory protection. AgentSafe classifies information by security levels, restricting sensitive data access to authorized agents. AgentSafe incorporates two components: ThreatSieve, which secures communication by verifying information authority and preventing impersonation, and HierarCache, an adaptive memory management system that defends against unauthorized access and malicious poisoning, representing the first systematic defense for agent memory. Experiments across various LLMs show that AgentSafe significantly boosts system resilience, achieving defense success rates above 80% under adversarial conditions. Additionally, AgentSafe demonstrates scalability, maintaining robust performance as agent numbers and information complexity grow. Results underscore effectiveness of AgentSafe in securing MAS and its potential for real-world application.</t>
+          <t>Urban mining recovery and reuse involve a complex system of multiple agents with independent interests across different stages. This study examines the dual-layer coordination among four key agents-supplying, recycling and sorting, reuse, and regulatory-using multi-period game theory and a heterogeneous social network model. By integrating these models with a multi-agent based simulation (MABS), we achieve bidirectional feedback and dynamic interactions. Our analysis under various policy scenarios reveals that non-cooperative strategies often dominate, but adjusting price schemes can effectively stimulate cooperative strategies among recycling and sorting agents with limited impact on other agents. Policy effects also vary based on agent personality matches. A gradual subsidy phase-out mechanism enhances the stability of collaborative evolution among recycling and sorting agents, while technical threshold subsidies promote technological learning, driving refined processing by reuse agents. Enhancing network effects through adjusting interaction willingness and market entry and exit rules increases network link probabilities but may counteract collaborative behaviors, whereas small groups within a certain range show better coordination and stability. In this study, a solid basis is laid for future research and implementation of effective multi-agent behaviors in urban mining, offering a valuable reference for stakeholders in urban resource management and policy-making.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1236,18 +1242,18 @@
         <v>0</v>
       </c>
       <c r="M11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1256,27 +1262,27 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scaling Large-Language-Model-based Multi-Agent Collaboration</t>
+          <t>Coordinating Artificial Intelligence and Bitcoin Mining Workloads: A Risk-Aware Distributional Multi-Agent Reinforcement Learning Approach</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cheng Qian; Zihao Xie; Yifei Wang; Wei Liu; Yu-Fan Dang; Zhuoyun Du; Weize Chen; Cheng Yang; Zhiyuan Liu; Maosong Sun</t>
+          <t>Ioannis T. Thomaidis; Panagiotis G. Giannopoulos; Thomas K. Dasaklis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>International Conference on Learning Representations</t>
+          <t>International Conference on Information, Intelligence, Systems and Applications</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1286,12 +1292,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2406.07155</t>
+          <t>10.1109/IISA66859.2025.11311340</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Recent breakthroughs in large language model-driven autonomous agents have revealed that multi-agent collaboration often surpasses each individual through collective reasoning. Inspired by the neural scaling law--increasing neurons enhances performance, this study explores whether the continuous addition of collaborative agents can yield similar benefits. Technically, we utilize directed acyclic graphs to organize agents into a multi-agent collaboration network (MacNet), upon which their interactive reasoning is topologically orchestrated for autonomous task solving. Extensive evaluations reveal that it effectively supports collaboration among over a thousand agents, with irregular topologies outperforming regular ones. We also identify a collaborative scaling law--the overall performance follows a logistic growth pattern as agents scale, with collaborative emergence occurring earlier than traditional neural emergence. We speculate this may be because scaling agents catalyzes their multidimensional considerations during interactive reflection and refinement, thereby producing more comprehensive artifacts. The code is available at https://github.com/OpenBMB/ChatDev/tree/macnet.</t>
+          <t>The rapid expansion of Artificial Intelligence (AI) workloads has created substantial energy requirements for contemporary data centers, which generate worries about infrastructure expansion and operational expenses and environmental sustainability. The worldwide shift toward renewable energy creates uncertainties in power supply that lead to grid instability and energy curtailment problems. This paper explores the synergistic convergence of AI compute infrastructure and Bitcoin (BTC) mining as a novel, energy-aware co-optimization framework. We propose a Distributional Multi-Agent Reinforcement Learning (MARL) system that dynamically allocates surplus energy between latency-sensitive AI jobs and highly flexible BTC mining operations. The proposed solution includes essential participants like renewable energy producers, energy management agents, AI clusters and BTC miners operating within a centralized training and decentralized execution paradigm. The simulation demonstrates that our MARL-driven methodology reduces the reduction in renewable energy by up to 65 % while maintaining high BTC mining profitability and stable grid demand and ensuring AI service level compliance. These findings suggest a path toward sustainable, intelligent energy computation ecosystems where AI and blockchain technologies operate not as competitors, but as complementary agents within a unified infrastructure.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1312,18 +1318,18 @@
         <v>0</v>
       </c>
       <c r="M12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1332,19 +1338,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AutoSCORE: Enhancing Automated Scoring with Multi-Agent Large Language Models via Structured Component Recognition</t>
+          <t>Multi-agent techniques for planning stripping operations and minimizing environmental risks in mining operations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yun Wang; Zhaojun Ding; Xuansheng Wu; Siyue Sun; Ninghao Liu; Xiaoming Zhai</t>
+          <t>N. L. Krasyukova; A. Z. Zubets; S. G. Eremin; A. Zubenko; A. M. Laffakh</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1352,7 +1358,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AAAI Conference on Artificial Intelligence</t>
+          <t>Mining Industry Journal (Gornay Promishlennost)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1362,12 +1368,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10.1609/aaai.v40i48.42123</t>
+          <t>10.30686/1609-9192-2025-1-170-176</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Automated scoring plays a crucial role in education by reducing the reliance on human raters and offering scalable and immediate evaluation of student work. While large language models (LLMs) have shown strong potential in this task, their use as end-to-end raters faces challenges such as low accuracy, prompt sensitivity, limited interpretability, and rubric misalignment, which hinder practical implementation. To address the limitations, we propose AutoSCORE, a multi-agent LLM framework enhancing automated scoring via rubric-aligned Structured COmponent REcognition. With two agents, AutoSCORE first extracts rubric-relevant components from student responses and encodes them into a structured representation (i.e., Scoring Rubric Component Extraction Agent), which is then used to assign final scores (i.e., Scoring Agent). This design ensures that model reasoning follows a human-like grading process, enhancing interpretability and robustness. We evaluate AutoSCORE on four benchmark datasets from the ASAP benchmark, using both proprietary and open-source LLMs (GPT-4o, LLaMA-3.1-8B, LLaMA-3.1-70B). Across diverse tasks and rubrics, AutoSCORE predominantly improves scoring accuracy, human-machine agreement (QWK, correlations), and reduces error metrics (MAE, RMSE) compared to single-agent baselines, with particularly strong benefits on complex, multidimensional rubrics, and especially large relative gains on smaller LLMs. These results demonstrate that structured component recognition combined with multi-agent design offers a scalable, reliable, and interpretable solution for automated scoring.</t>
+          <t>The research is focused on analyzing the potential of using the multi-agent techniques to optimize stripping operations and reduce the adverse environmental impact in the mining industry. The objective of the work is to develop a comprehensive model for planning of the stripping operations based on multi-agent systems with account of environmental factors. System analysis, simulation modeling, and multi-criteria optimization methods were used as the methodological basis. The empirical selection included data on 25 mining enterprises in Russia over the period of 2018-2023. The key results demonstrate that implementation of the multi-agent systems can shorten the stripping planning time by 27%, cut the volume of transported overburden by 18% and reduce CO2 emissions by 22%. The developed model provides an increase in the forecast accuracy up to 94% and an improvement in the overall efficiency of the stripping operations by 20-25%. The conclusions obtained are of high practical significance for the sustainable development of the mining sector and can serve as a basis for further research in the field of green technologies.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1385,21 +1391,21 @@
         <v>1</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1408,27 +1414,27 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CartoAgent: a multimodal large language model-powered multi-agent cartographic framework for map style transfer and evaluation</t>
+          <t>Vehicle Autonomy to Ecosystem Intelligence: A Systematic Review of Dynamic Vision Architectures in Surface Mining Operations</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chenglong Wang; Yu-Hao Kang; Zhao-Ya Gong; Peng-Jun Zhao; Yu Feng; Wen-Jia Zhang; Ge Li</t>
+          <t>Anti N.Y.D.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>International Journal of Geographical Information Science</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1438,17 +1444,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10.1080/13658816.2025.2507844</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Abstract The rapid development of generative artificial intelligence (GenAI) presents new opportunities to advance the cartographic process. Previous studies have either overlooked the artistic aspects of maps or faced challenges in creating both accurate and informative maps. In this study, we propose CartoAgent, a novel multi-agent cartographic framework powered by multimodal large language models (MLLMs). This framework simulates three key stages in cartographic practice: preparation, map design, and evaluation. At each stage, different MLLMs act as agents with distinct roles to collaborate, discuss, and utilize tools for specific purposes. In particular, CartoAgent leverages MLLMs’ visual aesthetic capability and world knowledge to generate maps that are both visually appealing and informative. By separating style from geographic data, it can focus on designing stylesheets without modifying the vector-based data, thereby ensuring geographic accuracy. As a result, the proposed CartoAgent could effectively produce maps that are not only visually appealing but also accurate and informative. We applied it to a specific task centered on map restyling, namely, map style transfer and evaluation. The effectiveness of this framework was validated through extensive experiments and a human evaluation study. CartoAgent can be extended to support a variety of cartographic design decisions and inform future integrations of GenAI in cartography.</t>
-        </is>
-      </c>
+          <t>10.3390/s26134258</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1458,24 +1460,24 @@
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1484,27 +1486,27 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Beyond Text: Implementing Multimodal Large Language Model-Powered Multi-Agent Systems Using a No-Code Platform</t>
+          <t>Research on optimized operation of multi-mine integrated energy system under double-layer game</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cheonsu Jeong</t>
+          <t>Li X.</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Journal of Intelligence and Information Systems</t>
+          <t>Meitan Xuebao Journal of the China Coal Society</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1514,17 +1516,13 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10.13088/jiis.2025.31.1.191</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>This study proposes the design and implementation of a multimodal LLM-based Multi-Agent System (MAS) leveraging a No-Code platform to address the practical constraints and significant entry barriers associated with AI adoption in enterprises. Advanced AI technologies, such as Large Language Models (LLMs), often pose challenges due to their technical complexity and high implementation costs, making them difficult for many organizations to adopt. To overcome these limitations, this research develops a No-Code-based Multi-Agent System designed to enable users without programming knowledge to easily build and manage AI systems. The study examines various use cases to validate the applicability of AI in business processes, including code generation from image-based notes, Advanced RAG-based question-answering systems, text-based image generation, and video generation using images and prompts. These systems lower the barriers to AI adoption, empowering not only professional developers but also general users to harness AI for significantly improved productivity and efficiency. By demonstrating the scalability and accessibility of No-Code platforms, this study advances the democratization of AI technologies within enterprises and validates the practical applicability of Multi-Agent Systems, ultimately contributing to the widespread adoption of AI across various industries.</t>
-        </is>
-      </c>
+          <t>10.13225/j.cnki.jccs.2025.1167</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1534,20 +1532,20 @@
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1560,27 +1558,27 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Large Language Model Based Multi-Agent System Augmented Complex Event Processing Pipeline for Internet of Multimedia Things</t>
+          <t>Digital-Twin and IoT-Enabled Closed-Loop Dispatch for Dynamic Ore-Grade Blending in Open-Pit Mining</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Talha Zeeshan; Abhishek Kumar; Susanna Pirttikangas; Sasu Tarkoma</t>
+          <t>Uchkun E.</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>Mining Metallurgy and Exploration</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1590,17 +1588,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2501.00906</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>This paper presents the development and evaluation of a Large Language Model (LLM), also known as foundation models, based multi-agent system framework for complex event processing (CEP) with a focus on video query processing use cases. The primary goal is to create a proof-of-concept (POC) that integrates state-of-the-art LLM orchestration frameworks with publish/subscribe (pub/sub) tools to address the integration of LLMs with current CEP systems. Utilizing the Autogen framework in conjunction with Kafka message brokers, the system demonstrates an autonomous CEP pipeline capable of handling complex workflows. Extensive experiments evaluate the system's performance across varying configurations, complexities, and video resolutions, revealing the trade-offs between functionality and latency. The results show that while higher agent count and video complexities increase latency, the system maintains high consistency in narrative coherence. This research builds upon and contributes to, existing novel approaches to distributed AI systems, offering detailed insights into integrating such systems into existing infrastructures.</t>
-        </is>
-      </c>
+          <t>10.1007/s42461-026-01667-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1610,24 +1604,24 @@
         <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1636,27 +1630,27 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Automated building energy modeling for energy retrofits using a large language model-based multi-agent framework</t>
+          <t>Large Language Model Agents in Dynamic Mine Planning: Challenges, Opportunities, and Future Directions</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jie Lu; Zeyu Zheng; Max Langtry; Monty Jackson; Yang Zhao; Chenxin Feng; Ruqian Zhang; Chaobo Zhang; Jian Zhang; R. Choudhary</t>
+          <t>Nunes R.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>iScience</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1666,17 +1660,13 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.1016/j.isci.2025.113867</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Summary Building energy modeling is critical for retrofit design, but it is labor-intensive. We present Data2BEM (Data to Building Energy Model), a large language model-based multi-agent framework that parses architectural drawings, specifications, and sensor data to automatically generate and calibrate building energy simulations. Applied to an existing University of Cambridge office building, Data2BEM produced a calibrated model meeting industry accuracy benchmarks and enabled the assessment of heat-electrification retrofits. Relative to professional practice, the system reduced total modeling time by over 90% (48 min versus 8–32 h) with minimal human input. The workflow integrates information extraction, model generation, and data-driven calibration, delivering end-to-end automation while accurately reflecting measured performance. These results indicate that large language model-driven multi-agent methods can accelerate retrofit analysis, lowering expertise and time barriers for practitioners and supporting scalable pathways to building-sector decarbonization.</t>
-        </is>
-      </c>
+          <t>10.1109/access.2026.3714775</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1689,21 +1679,21 @@
         <v>1</v>
       </c>
       <c r="L17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
       </c>
       <c r="N17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO-LLM</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1712,19 +1702,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rapid and automated alloy design with graph neural network-powered large language model-driven multi-agent AI</t>
+          <t>Real-time autonomous truck dispatch strategy for multi-arterial haulage systems in open-pit coal mines</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alireza Ghafarollahi; Markus J. Buehler</t>
+          <t>Luan B.</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1732,7 +1722,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MRS bulletin</t>
+          <t>Meitan Xuebao Journal of the China Coal Society</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1742,17 +1732,13 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10.1557/s43577-025-00953-4</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>A multi-agent artificial intelligence (AI) model is developed to automate the discovery of new metallic alloys, integrating multimodal data and external knowledge, including insights from physics via atomistic simulations. The system consists of (a) large language models (LLMs) for tasks such as reasoning and planning, (b) AI agents with distinct roles collaborating dynamically, and (c) a newly developed graph neural network (GNN) model for rapid retrieval of physical properties. We chose the ternary NbMoTa body-centered-cubic alloy as our model system and developed the GNN to predict two fundamental materials properties: the Peierls barrier and the solute/screw dislocation interaction energy. Our GNN model efficiently predicts these properties, reducing reliance on costly brute-force calculations and alleviating the computational demands on the multi-agent system. By combining the predictive capabilities of GNNs with the collaborative intelligence of LLM-driven reasoning agents, the system autonomously explores vast alloy design spaces, identifies trends in atomic-scale properties, and predicts macroscale mechanical strength, as demonstrated by several computational experiments. This synergistic approach accelerates the discovery of advanced alloys and holds promise for broader applications in other complex systems, marking a step forward in automated materials discovery and design. Traditional deep learning models, such as graph neural networks and convolutional neural networks, operate within the confines of their training data sets, making single-step inferences for regression or classification. Our work introduces a multi-agent strategy that transcends these limitations by integrating deep learning with reasoning and decision-making capabilities. This intelligent system actively interprets results, determines subsequent actions, and iteratively refines predictions, accelerating the materials design process. We demonstrate its effectiveness in exploring the vast compositional space of a ternary alloy, where the model dynamically solicits data, analyzes trends, generates visualizations, and derives insights into materials behavior. By enabling accurate predictions of key alloy characteristics, our approach advances the discovery of novel metallic systems and underscores the critical role of solid-solution alloying. More broadly, it represents a major step toward integrating artificial intelligence with scientific reasoning, moving closer to artificial general intelligence in engineering. This paradigm shift has profound implications for materials science, enabling more efficient, autonomous, and intelligent exploration of complex materials spaces.</t>
-        </is>
-      </c>
+          <t>10.13225/j.cnki.jccs.2025.0044</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1762,20 +1748,20 @@
         <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1788,19 +1774,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2025; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Large language model-enabled multi-agent self-organised approach for personalised rehabilitation assistive devices design</t>
+          <t>Automated Daily Production Report Generation for Coal Mine Dispatch Rooms Based on Distil-LLM and Autogen Agents</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wei-Bin Zhuang; Xinyu Pan; Sijie Wen; Weigang Yu; Xin-Yu Li; Jinsong Bao</t>
+          <t>Meng Q.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1808,27 +1794,23 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>International Journal of Production Research</t>
+          <t>Spml 2025 Proceedings of 2025 IEEE 8th International Conference on Signal Processing and Machine Learning</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>journal</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.1080/00207543.2025.2509155</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>With the increasing prevalence of age-related diseases among the elderly, escalating disability rates resulting from chronic illnesses, and heightened public health awareness, there is a growing demand for personalised design of rehabilitation assistive devices (RADs). Conventional product design methods have shown significant limitations in addressing the diversity and individuality of user needs. Therefore, leveraging large language models (LLM) to self-organise multi-agents, an innovative method for designing personalised RADs, called LLM-PDAgents, is proposed in this manuscript. Initially, a knowledge graph (KG) was constructed with the relationship among ‘phenomenon-symptom-function-behaviour-structure', establishing a chain-of-thought for product design knowledge within multi-agents. Subsequently, a thinking mechanism for task planning in the self-organised process of multi-agents was developed, which emulates the processes of planning, execution, and monitoring in product design. Ultimately, a multi-tiered progressive reflection strategy was devised to iteratively refine the product design, fostering a continuous optimization on the design solution until user satisfaction is achieved. Taking the real-world design of knee joint RADs as an example, LLM-PDAgents significantly improved the procedure and quality of the whole design process, and its outcomes showed merits on economic viability, manufacturing feasibility, user pertinence, and generated costs, indicating an efficient and reliable approach for the personalised design of RADs.</t>
-        </is>
-      </c>
+          <t>10.1109/SPML66318.2025.11199818</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1838,24 +1820,24 @@
         <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
       </c>
       <c r="N19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO-LLM</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1864,27 +1846,27 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='conference'; categoria='MAS-DESPACHO-MINERO-LLM'; year=2025; se omitio pendiente por venue_type=conference por categoria de alcance ampliado; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Large Language Model based Multi-Agents: A Survey of Progress and Challenges</t>
+          <t>Hierarchical multiagent reinforcement learning for sustainable truck dispatching in open-pit mining</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Taicheng Guo; Xiuying Chen; Yaqi Wang; Ruidi Chang; Shichao Pei; N. Chawla; Olaf Wiest; Xiangliang Zhang</t>
+          <t>Zhao K.</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>International Joint Conference on Artificial Intelligence</t>
+          <t>Transportmetrica A Transport Science</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1894,17 +1876,13 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2402.01680</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Large Language Models (LLMs) have achieved remarkable success across a wide array of tasks. Due to their notable capabilities in planning and reasoning, LLMs have been utilized as autonomous agents for the automatic execution of various tasks. Recently, LLM-based agent systems have rapidly evolved from single-agent planning or decision-making to operating as multi-agent systems, enhancing their ability in complex problem-solving and world simulation. To offer an overview of this dynamic field, we present this survey to offer an in-depth discussion on the essential aspects and challenges of LLM-based multi-agent (LLM-MA) systems. Our objective is to provide readers with an in-depth understanding of these key points: the domains and settings where LLM-MA systems operate or simulate; the profiling and communication methods of these agents; and the means by which these agents develop their skills. For those interested in delving into this field, we also summarize the commonly used datasets or benchmarks. To keep researchers updated on the latest studies, we maintain an open-source GitHub repository (github.com/taichengguo/LLM_MultiAgents_Survey_Papers), dedicated to outlining the research of LLM-MA research.</t>
-        </is>
-      </c>
+          <t>10.1080/23249935.2025.2522360</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -1914,20 +1892,20 @@
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1940,27 +1918,27 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2025; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ProtAgents: protein discovery via large language model multi-agent collaborations combining physics and machine learning</t>
+          <t>Data-oriented distributed demand response optimization with global inequality constraints based on multi-agent system</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alireza Ghafarollahi; Markus J. Buehler</t>
+          <t>Hao, Ran; Lu, Tianguang; Ai, Qian; He, Hongyin</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Digital Discovery</t>
+          <t>INTERNATIONAL JOURNAL OF ELECTRICAL POWER &amp; ENERGY SYSTEMS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1970,17 +1948,13 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2402.04268</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Designing de novo proteins beyond those found in nature holds significant promise for advancements in both scientific and engineering applications. Current methodologies for protein design often rely on AI-based models, such as surrogate models that address end-to-end problems by linking protein structure to material properties or vice versa. However, these models frequently focus on specific material objectives or structural properties, limiting their flexibility when incorporating out-of-domain knowledge into the design process or comprehensive data analysis is required. In this study, we introduce ProtAgents, a platform for de novo protein design based on Large Language Models (LLMs), where multiple AI agents with distinct capabilities collaboratively address complex tasks within a dynamic environment. The versatility in agent development allows for expertise in diverse domains, including knowledge retrieval, protein structure analysis, physics-based simulations, and results analysis. The dynamic collaboration between agents, empowered by LLMs, provides a versatile approach to tackling protein design and analysis problems, as demonstrated through diverse examples in this study. The problems of interest encompass designing new proteins, analyzing protein structures and obtaining new first-principles data – natural vibrational frequencies – via physics simulations. The concerted effort of the system allows for powerful automated and synergistic design of de novo proteins with targeted mechanical properties. The flexibility in designing the agents, on one hand, and their capacity in autonomous collaboration through the dynamic LLM-based multi-agent environment on the other hand, unleashes great potentials of LLMs in addressing multi-objective materials problems and opens up new avenues for autonomous materials discovery and design.</t>
-        </is>
-      </c>
+          <t>10.1016/j.ijepes.2021.107025</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -1993,17 +1967,17 @@
         <v>1</v>
       </c>
       <c r="L21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2016,27 +1990,27 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Intention-behavior consistency-based automated failure attribution for LLM-driven multi-agent systems</t>
+          <t>Real-time multi-agent fleet management strategy for autonomous underground mines vehicles</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wu H.</t>
+          <t>Gamache, M.; Basilico, G.; Frayret, J. -M.; Riopel, D.</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Expert Systems with Applications</t>
+          <t>INTERNATIONAL JOURNAL OF MINING RECLAMATION AND ENVIRONMENT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2046,13 +2020,13 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10.1016/j.eswa.2026.133044</t>
+          <t>10.1080/17480930.2023.2236880</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2065,21 +2039,21 @@
         <v>1</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2088,27 +2062,27 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2023; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PenExpert: A multi-agent hybrid LLM–expert system framework for autonomous penetration testing</t>
+          <t>Transition to intelligent fleet management systems in open pit mines: A critical review on application of reinforcement-learning-based systems</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Li Z.</t>
+          <t>Hazrathosseini, Arman; Moradi Afrapoli, Ali</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Expert Systems with Applications</t>
+          <t>MINING TECHNOLOGY-TRANSACTIONS OF THE INSTITUTIONS OF MINING AND METALLURGY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2118,13 +2092,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10.1016/j.eswa.2026.133284</t>
+          <t>10.1177/25726668231222998</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2134,20 +2108,20 @@
         <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2160,27 +2134,27 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2024; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hierarchical Multi-agent Large Language Model Reasoning for Autonomous Heterogeneous Catalyst Discovery</t>
+          <t>Distributed predefined-time algorithms for optimal solution seeking in multi-agent systems subject to input disturbances</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rothfarb S.</t>
+          <t>Xu, Jing-Zhe; Liu, Zhi-Wei; Ge, Ming-Feng; Yang, Tao; Chi, Ming; He, Dingxin</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Npj Computational Materials</t>
+          <t>AUTOMATICA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2190,13 +2164,13 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10.1038/s41524-026-02139-1</t>
+          <t>10.1016/j.automatica.2025.112139</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2209,17 +2183,17 @@
         <v>1</v>
       </c>
       <c r="L24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2232,19 +2206,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Large language model-based multi-agent systems for automated foundation design: router-driven task classification and expert selection framework</t>
+          <t>Learning-based dispatching system with trajectory optimisation for autonomous mining transportation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Youwai S.</t>
+          <t>Pei, Shuwei; Yang, Jue; Gong, Zeyu</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2252,7 +2226,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI in Civil Engineering</t>
+          <t>INTERNATIONAL JOURNAL OF MINING RECLAMATION AND ENVIRONMENT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2262,13 +2236,13 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10.1007/s43503-026-00088-8</t>
+          <t>10.1080/17480930.2025.2486316</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2278,20 +2252,20 @@
         <v>0</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2304,27 +2278,27 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=false; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; se omitio exclusion por mas=False por categoria de alcance ampliado; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A hierarchical multi-agent reinforcement learning framework with high-level guidance from large language models</t>
+          <t>Exact Prescribed-Time Distributed Optimization for Second-Order Multi-Agent Systems: A Time-Switching Control Strategy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bai J.</t>
+          <t>Duan, Suna; Jia, Xinchun; Li, Hongpeng; Lv, Teng; Chi, Xiaobo</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>IEEE TRANSACTIONS ON NETWORK SCIENCE AND ENGINEERING</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2334,13 +2308,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10.1038/s41598-026-54971-6</t>
+          <t>10.1109/TNSE.2025.3573733</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I26" t="b">
@@ -2353,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="L26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
@@ -2367,7 +2341,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2376,19 +2350,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>When collaboration fails: persuasion driven adversarial influence in multi agent large language model debate</t>
+          <t>Reinforcement Learning-Driven Negotiation in a Multi-Agent System for Truck Dispatching in Open-Pit Mining</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kraidia I.</t>
+          <t>Herzog, Otthein; Icarte-Ahumada, Gabriel; Arratia, Daniel; Lucero, Cristian</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2396,7 +2370,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>APPLIED SCIENCES-BASEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2406,13 +2380,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.1038/s41598-026-42705-7</t>
+          <t>10.3390/app16052343</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I27" t="b">
@@ -2425,21 +2399,21 @@
         <v>1</v>
       </c>
       <c r="L27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2448,19 +2422,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Multi-agent SEA: step-wise evidence acquisition for multimodal financial reasoning</t>
+          <t>Centralized Evolutionary Optimization and Decentralized Agent-Based Scheduling for Open-Pit Mine Dispatching</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deng S.</t>
+          <t>Icarte-Ahumada, Gabriel; Goyo, Manuel; Godoy, Victor; Herzog, Otthein</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2468,7 +2442,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Information Fusion</t>
+          <t>APPLIED SCIENCES-BASEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2478,13 +2452,13 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.1016/j.inffus.2026.104550</t>
+          <t>10.3390/app16157595</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I28" t="b">
@@ -2497,21 +2471,21 @@
         <v>1</v>
       </c>
       <c r="L28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
       </c>
       <c r="N28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2520,19 +2494,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Safe integration of Large Language Models into industrial process control: a multi-agent architecture with P&amp;ID-grounded validation</t>
+          <t>Intention-behavior consistency-based automated failure attribution for LLM-driven multi-agent systems</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Schall D.</t>
+          <t>Wu H.</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2540,7 +2514,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Autonomous Intelligent Systems</t>
+          <t>Expert Systems with Applications</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2550,7 +2524,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10.1007/s43684-026-00136-1</t>
+          <t>10.1016/j.eswa.2026.133044</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -2599,12 +2573,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Public opinion dissemination simulation based on large language model multi-agent systems</t>
+          <t>PenExpert: A multi-agent hybrid LLM–expert system framework for autonomous penetration testing</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lan H.</t>
+          <t>Li Z.</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2612,7 +2586,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Expert Systems with Applications</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2622,7 +2596,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10.1038/s41598-026-44206-z</t>
+          <t>10.1016/j.eswa.2026.133284</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -2644,18 +2618,18 @@
         <v>0</v>
       </c>
       <c r="M30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2664,19 +2638,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Towards higher quality and fewer hallucinations: A multi-agent collaboration framework for LLMs</t>
+          <t>Agentic publications: redesigning scientific publishing in the age of thinking large language models</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shen S.</t>
+          <t>Pugliese R.</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2684,7 +2658,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Information Processing and Management</t>
+          <t>Journal of Documentation</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2694,7 +2668,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10.1016/j.ipm.2026.104953</t>
+          <t>10.1108/JD-07-2025-0207</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -2716,18 +2690,18 @@
         <v>0</v>
       </c>
       <c r="M31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2736,19 +2710,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PublicAgent: Multi-agent design principles from an LLM-based open data analysis framework</t>
+          <t>Hierarchical Multi-agent Large Language Model Reasoning for Autonomous Heterogeneous Catalyst Discovery</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Montazeri S.</t>
+          <t>Rothfarb S.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2756,7 +2730,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Digital Engineering</t>
+          <t>Npj Computational Materials</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2766,7 +2740,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.1016/j.dte.2026.100136</t>
+          <t>10.1038/s41524-026-02139-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -2815,12 +2789,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAP: evaluation and multi-agent enhancement of large language models for inpatient pathways</t>
+          <t>Large language model-based multi-agent systems for automated foundation design: router-driven task classification and expert selection framework</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chen Z.</t>
+          <t>Youwai S.</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2828,7 +2802,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Npj Health Systems</t>
+          <t>AI in Civil Engineering</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2838,7 +2812,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10.1038/s44401-026-00085-0</t>
+          <t>10.1007/s43503-026-00088-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2860,18 +2834,18 @@
         <v>0</v>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2880,19 +2854,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Automated summarization of software documents: an LLM-based multi-agent approach</t>
+          <t>A hierarchical multi-agent reinforcement learning framework with high-level guidance from large language models</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nguyen D.S.H.</t>
+          <t>Bai J.</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2900,7 +2874,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Automated Software Engineering</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2910,7 +2884,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10.1007/s10515-025-00588-4</t>
+          <t>10.1038/s41598-026-54971-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2959,32 +2933,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Short Duration Aggregate Statistical Model Checking for Multi-Agent Systems</t>
+          <t>When collaboration fails: persuasion driven adversarial influence in multi agent large language model debate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yenda, Ramesh; Rao, M. V. Panduranga</t>
+          <t>Kraidia I.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lecture Notes in Computer Science</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-69322-0_32</t>
+          <t>10.1038/s41598-026-42705-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>wos</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I35" t="b">
@@ -3000,18 +2978,18 @@
         <v>0</v>
       </c>
       <c r="M35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3020,27 +2998,27 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>An action language for multi-agent domains</t>
+          <t>Multi-agent SEA: step-wise evidence acquisition for multimodal financial reasoning</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Baral, Chitta; Gelfond, Gregory; Pontelli, Enrico; Tran Cao Son</t>
+          <t>Deng S.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE</t>
+          <t>Information Fusion</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3050,13 +3028,13 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10.1016/j.artint.2021.103601</t>
+          <t>10.1016/j.inffus.2026.104550</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>wos</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I36" t="b">
@@ -3072,18 +3050,18 @@
         <v>0</v>
       </c>
       <c r="M36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3092,27 +3070,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Describing Structure and Complex Interactions in Multi-Agent-Based Industrial Cyber-Physical Systems</t>
+          <t>Safe integration of Large Language Models into industrial process control: a multi-agent architecture with P&amp;ID-grounded validation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ribeiro, Luis; Gomes, Luis</t>
+          <t>Schall D.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IEEE ACCESS</t>
+          <t>Autonomous Intelligent Systems</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3122,13 +3100,13 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.1109/ACCESS.2021.3127344</t>
+          <t>10.1007/s43684-026-00136-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>wos</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3144,18 +3122,18 @@
         <v>0</v>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3164,35 +3142,43 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Multi-Agent Reinforcement Learning is A Sequence Modeling Problem</t>
+          <t>Public opinion dissemination simulation based on large language model multi-agent systems</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wen, Muning; Kuba, Jakub Grudzien; Lin, Runji; Zhang, Weinan; Wen, Ying; Wang, Jun; Yang, Yaodong</t>
+          <t>Lan H.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ADVANCES IN NEURAL INFORMATION PROCESSING SYSTEMS 35 (NEURIPS 2022)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-026-44206-z</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>wos</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3208,18 +3194,18 @@
         <v>0</v>
       </c>
       <c r="M38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3228,27 +3214,27 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DeConNet: Deep Neural Network Model to Solve the Multi-Job Assignment Problem in the Multi-Agent System</t>
+          <t>Towards higher quality and fewer hallucinations: A multi-agent collaboration framework for LLMs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lee, Jungwoo; Choi, Youngho; Suh, Jinho</t>
+          <t>Shen S.</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>APPLIED SCIENCES-BASEL</t>
+          <t>Information Processing and Management</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3258,13 +3244,13 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.3390/app12115454</t>
+          <t>10.1016/j.ipm.2026.104953</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>wos</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I39" t="b">
@@ -3300,27 +3286,27 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hierarchical multiagent reinforcement learning for sustainable truck dispatching in open-pit mining</t>
+          <t>PublicAgent: Multi-agent design principles from an LLM-based open data analysis framework</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zhao K.</t>
+          <t>Montazeri S.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Transportmetrica A Transport Science</t>
+          <t>Digital Engineering</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3330,7 +3316,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10.1080/23249935.2025.2522360</t>
+          <t>10.1016/j.dte.2026.100136</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -3349,21 +3335,21 @@
         <v>1</v>
       </c>
       <c r="L40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>MAS-DESPACHO-MINERO</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3372,27 +3358,27 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data-oriented distributed demand response optimization with global inequality constraints based on multi-agent system</t>
+          <t>Automated summarization of software documents: an LLM-based multi-agent approach</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hao, Ran; Lu, Tianguang; Ai, Qian; He, Hongyin</t>
+          <t>Nguyen D.S.H.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INTERNATIONAL JOURNAL OF ELECTRICAL POWER &amp; ENERGY SYSTEMS</t>
+          <t>Automated Software Engineering</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3402,13 +3388,13 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10.1016/j.ijepes.2021.107025</t>
+          <t>10.1007/s10515-025-00588-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>wos</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3424,18 +3410,18 @@
         <v>0</v>
       </c>
       <c r="M41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3444,27 +3430,27 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Real-time multi-agent fleet management strategy for autonomous underground mines vehicles</t>
+          <t>iDesignGPT enhances conceptual design via large language model agentic workflows</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gamache, M.; Basilico, G.; Frayret, J. -M.; Riopel, D.</t>
+          <t>Liu S.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INTERNATIONAL JOURNAL OF MINING RECLAMATION AND ENVIRONMENT</t>
+          <t>Nature Communications</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3474,13 +3460,13 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10.1080/17480930.2023.2236880</t>
+          <t>10.1038/s41467-026-68672-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>wos</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I42" t="b">
@@ -3496,18 +3482,18 @@
         <v>0</v>
       </c>
       <c r="M42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3516,37 +3502,33 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2023; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Distributed predefined-time algorithms for optimal solution seeking in multi-agent systems subject to input disturbances</t>
+          <t>Short Duration Aggregate Statistical Model Checking for Multi-Agent Systems</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Xu, Jing-Zhe; Liu, Zhi-Wei; Ge, Ming-Feng; Yang, Tao; Chi, Ming; He, Dingxin</t>
+          <t>Yenda, Ramesh; Rao, M. V. Panduranga</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AUTOMATICA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>Lecture Notes in Computer Science</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10.1016/j.automatica.2025.112139</t>
+          <t>10.1007/978-3-030-69322-0_32</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -3588,27 +3570,27 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Intelligent Scheduling in Open-Pit Mining: A Multi-Agent System with Reinforcement Learning</t>
+          <t>Agents and Robots for Reliable Engineered Autonomy:A Perspective from the Organisers of AREA 2020</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Icarte-Ahumada, Gabriel; Herzog, Otthein</t>
+          <t>Cardoso, Rafael C.; Ferrando, Angelo; Briola, Daniela; Menghi, Claudio; Ahlbrecht, Tobias</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MACHINES</t>
+          <t>JOURNAL OF SENSOR AND ACTUATOR NETWORKS</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3618,7 +3600,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.3390/machines13050350</t>
+          <t>10.3390/jsan10020033</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -3637,21 +3619,21 @@
         <v>1</v>
       </c>
       <c r="L44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
       <c r="N44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>MAS-DESPACHO-MINERO</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3660,27 +3642,27 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Exact Prescribed-Time Distributed Optimization for Second-Order Multi-Agent Systems: A Time-Switching Control Strategy</t>
+          <t>An action language for multi-agent domains</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Duan, Suna; Jia, Xinchun; Li, Hongpeng; Lv, Teng; Chi, Xiaobo</t>
+          <t>Baral, Chitta; Gelfond, Gregory; Pontelli, Enrico; Tran Cao Son</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IEEE TRANSACTIONS ON NETWORK SCIENCE AND ENGINEERING</t>
+          <t>ARTIFICIAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3690,7 +3672,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10.1109/TNSE.2025.3573733</t>
+          <t>10.1016/j.artint.2021.103601</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -3712,18 +3694,18 @@
         <v>0</v>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3732,27 +3714,27 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Reinforcement Learning-Driven Negotiation in a Multi-Agent System for Truck Dispatching in Open-Pit Mining</t>
+          <t>Describing Structure and Complex Interactions in Multi-Agent-Based Industrial Cyber-Physical Systems</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Herzog, Otthein; Icarte-Ahumada, Gabriel; Arratia, Daniel; Lucero, Cristian</t>
+          <t>Ribeiro, Luis; Gomes, Luis</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>APPLIED SCIENCES-BASEL</t>
+          <t>IEEE ACCESS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3762,7 +3744,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10.3390/app16052343</t>
+          <t>10.1109/ACCESS.2021.3127344</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -3781,21 +3763,21 @@
         <v>1</v>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>MAS-DESPACHO-MINERO</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3804,39 +3786,31 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Centralized Evolutionary Optimization and Decentralized Agent-Based Scheduling for Open-Pit Mine Dispatching</t>
+          <t>Multi-Agent Reinforcement Learning is A Sequence Modeling Problem</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Icarte-Ahumada, Gabriel; Goyo, Manuel; Godoy, Victor; Herzog, Otthein</t>
+          <t>Wen, Muning; Kuba, Jakub Grudzien; Lin, Runji; Zhang, Weinan; Wen, Ying; Wang, Jun; Yang, Yaodong</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>APPLIED SCIENCES-BASEL</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>10.3390/app16157595</t>
-        </is>
-      </c>
+          <t>ADVANCES IN NEURAL INFORMATION PROCESSING SYSTEMS 35 (NEURIPS 2022)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
@@ -3856,18 +3830,18 @@
         <v>1</v>
       </c>
       <c r="M47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3876,27 +3850,27 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-LLM'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DruGagent: Multi-Agent Large Language Model-Based Reasoning for Drug-Target Interaction Prediction</t>
+          <t>DeConNet: Deep Neural Network Model to Solve the Multi-Job Assignment Problem in the Multi-Agent System</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yoshitaka Inoue; Tianci Song; Xinlin Wang; Augustin Luna; Tianfan Fu</t>
+          <t>Lee, Jungwoo; Choi, Youngho; Suh, Jinho</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>APPLIED SCIENCES-BASEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3904,15 +3878,15 @@
           <t>journal</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Advancements in large language models (LLMs) allow them to address diverse questions using human-like interfaces. Still, limitations in their training prevent them from answering accurately in scenarios that could benefit from multiple perspectives. Multi-agent systems allow the resolution of questions to enhance result consistency and reliability. While drug-target interaction (DTI) prediction is important for drug discovery, existing approaches face challenges due to complex biological systems and the lack of interpretability needed for clinical applications. DrugAgent is a multi-agent LLM system for DTI prediction that combines multiple specialized perspectives with transparent reasoning. Our system adapts and extends existing multi-agent frameworks by (1) applying coordinator-based architecture to the DTI domain, (2) integrating domain-specific data sources, including ML predictions, knowledge graphs, and literature evidence, and (3) incorporating Chain-of-Thought (CoT) and ReAct (Reason+Act) frameworks for transparent DTI reasoning. We conducted comprehensive experiments using a kinase inhibitor dataset, where our multi-agent LLM method outperformed the non-reasoning multi-agent model (GPT-4o mini) by 45% in F1 score (0.514 vs 0.355). Through ablation studies, we demonstrated the contributions of each agent, with the AI agent being the most impactful, followed by the KG agent and search agent. Most importantly, our approach provides detailed, human-interpretable reasoning for each prediction by combining evidence from multiple sources - a critical feature for biomedical applications where understanding the rationale behind predictions is essential for clinical decision-making and regulatory compliance. Code is available at https://anonymous.4open.science/r/DrugAgent-B2EA.</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10.3390/app12115454</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -3925,17 +3899,17 @@
         <v>1</v>
       </c>
       <c r="L48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -3948,53 +3922,39 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Schema-Guided Scene-Graph Reasoning Based on Multi-Agent Large Language Model System</t>
+          <t>Languages of Distributed Reaction Systems</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yi-Ye Chen; Harpreet Sawhney; N. Gyde; Ya-Nan Jian; Jack Saunders; Patricio Vela; Benjamin E. Lundell</t>
+          <t>Ciencialova, Lucie; Cienciala, Ludek; Csuhaj-Varju, Erzsebet</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AAAI Conference on Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>Lecture Notes in Computer Science</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10.1609/aaai.v40i36.40285</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Scene graphs have emerged as a structured and serializable environment representation for grounded spatial reasoning with Large Language Models (LLMs).
- In this work, we propose SG2, an iterative Schema-Guided Scene-Graph reasoning framework based on multi-agent LLMs.
- The agents are grouped into two modules: a (1) Reasoner module for abstract task planning and graph information queries generation, and a (2) Retriever module for extracting corresponding graph information based on code-writing following the queries.
- Two modules collaborate iteratively, enabling sequential reasoning and adaptive attention to graph information.
- The scene graph schema, prompted to both modules, serves to not only streamline both reasoning and retrieval process, but also guide the cooperation between two modules.
- This eliminates the need to prompt LLMs with full graph data, reducing the chance of hallucination due to irrelevant information.
- Through experiments in multiple simulation environments, we show that our framework surpasses existing LLM-based approaches and baseline single-agent, tool-based Reason-while-Retrieve strategy in numerical Q&amp;A and planning tasks.</t>
-        </is>
-      </c>
+          <t>10.1007/978-3-031-13502-6_5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I49" t="b">
@@ -4030,47 +3990,39 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-LLM'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bridging Literature and the Universe Via A Multi-Agent Large Language Model System</t>
+          <t>The Survey of Object-Oriented Software Programming Language from a Heterogeneous Cluster Programming Viewpoint</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Xiaowen Zhang; Zhenyu Bi; Patrick Lachance; Xuan Wang; T. Matteo; R. Croft</t>
+          <t>Brandejsky, Tomas; Hrbek, Vaclav</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Proceedings of The 14th International Joint Conference on Natural Language Processing and The 4th Conference of the Asia-Pacific Chapter of the Association for Computational Linguistics: System Demonstrations</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>Lecture Notes in Networks and Systems</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2507.08958</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>As cosmological simulations and their associated software become increasingly complex, physicists face the challenge of searching through vast amounts of literature and user manuals to extract simulation parameters from dense academic papers, each using different models and formats. Translating these parameters into executable scripts remains a time-consuming and error-prone process. To improve efficiency in physics research and accelerate the cosmological simulation process, we introduce SimAgents, a multi-agent system designed to automate both parameter configuration from the literature and preliminary analysis for cosmology research. SimAgents is powered by specialized LLM agents capable of physics reasoning, simulation software validation, and tool execution. These agents collaborate through structured communication, ensuring that extracted parameters are physically meaningful, internally consistent, and software-compliant. We also construct a cosmological parameter extraction evaluation dataset by collecting over 40 simulations in published papers from Arxiv and leading journals that cover diverse simulation types. Experiments on the dataset demonstrate a strong performance of SimAgents, highlighting its effectiveness and potential to accelerate scientific research for physicists. Our demonstration video is available at: https://youtu.be/w1zLpm_CaWA. The complete system and dataset are publicly available at https://github.com/xwzhang98/SimAgents.</t>
-        </is>
-      </c>
+          <t>10.1007/978-3-031-09070-7_29</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I50" t="b">
@@ -4106,19 +4058,19 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-LLM'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Debate or Vote: Which Yields Better Decisions in Multi-Agent Large Language Models?</t>
+          <t>Research on collaborative scheduling strategies of multi-agent agricultural machinery groups</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hyeong Kyu Choi; Xiaojin Zhu; Yixuan Li</t>
+          <t>Ziyi Wang; Fan Zhang; Shijing Ma; Hailong Wang; Shunyao Zhang; Xiao-Zhong Gao</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4126,7 +4078,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Neural Information Processing Systems</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4136,12 +4088,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2508.17536</t>
+          <t>10.1038/s41598-025-93848-y</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Multi-Agent Debate~(MAD) has emerged as a promising paradigm for improving the performance of large language models through collaborative reasoning. Despite recent advances, the key factors driving MAD's effectiveness remain unclear. In this work, we disentangle MAD into two key components--Majority Voting and inter-agent Debate--and assess their respective contributions. Through extensive experiments across seven NLP benchmarks, we find that Majority Voting alone accounts for most of the performance gains typically attributed to MAD. To explain this, we propose a theoretical framework that models debate as a stochastic process. We prove that it induces a martingale over agents'belief trajectories, implying that debate alone does not improve expected correctness. Guided by these insights, we demonstrate that targeted interventions, by biasing the belief update toward correction, can meaningfully enhance debate effectiveness. Overall, our findings suggest that while MAD has potential, simple ensembling methods remain strong and more reliable alternatives in many practical settings. Code is released in https://github.com/deeplearning-wisc/debate-or-vote.</t>
+          <t>Addressing the challenges of high scheduling costs and low efficiency in the collaborative operations of agricultural machinery across multiple dispatch centers, this paper develops a scheduling model designed to minimize total costs. It introduces a Multi-Center and Multi-Machine Path Planning Algorithm Based on Deep Reinforcement Learning (MCMPP-DRL). Firstly, a deep reinforcement learning environment is established, and a policy network utilizing the attention mechanism is designed. Subsequently, the network model is trained to improve its solution capabilities using the policy gradient algorithm (REINFORCE). Finally, the solution is optimized through a local search strategy. In this study, three dispatch centers were selected within the maize growing area of Hebei Province, and comparative analyses were conducted for 20, 40, 50, 100 and 120 farmlands, respectively.The results indicate that the MCMPP-DRL algorithm achieves a reduction in total scheduling costs of at least 9.66%, 14.34% and 24.41% compared to Ant Colony Optimization (ACO), Simulated Annealing (SA) and Genetic Algorithms(GA), respectively.The significant optimization in scheduling costs demonstrates that the MCMPP-DRL algorithm establishes a robust theoretical foundation and offers technical support for addressing complex scheduling problems involving multiple dispatch centers and multiple.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4159,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="L51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4173,7 +4125,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4189,12 +4141,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Auto-TA: Towards Scalable Automated Thematic Analysis (TA) via Multi-Agent Large Language Models with Reinforcement Learning</t>
+          <t>Intelligent scheduling control for coordinated passing of multiple autonomous trucks at intersections in open-pit coal mines via enhanced multi-agent reinforcement learning</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Seungjun Yi; Joakim Nguyen; Hui-Rong Xu; Terence Lim; Andrew Well; Mia K. Markey; Ying Ding</t>
+          <t>Boyu Luan; Yufeng Xiao; Wei Zhou; Hairong Zhou; Xiangcheng Lu; Zhihui Han</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4202,7 +4154,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>Journal of Computational Design and Engineering</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4212,12 +4164,13 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2506.23998</t>
+          <t>10.1093/jcde/qwaf140</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Congenital heart disease (CHD) presents complex, lifelong challenges often underrepresented in traditional clinical metrics. While unstructured narratives offer rich insights into patient and caregiver experiences, manual thematic analysis (TA) remains labor-intensive and unscalable. We propose a fully automated large language model (LLM) pipeline that performs end-to-end TA on clinical narratives, which eliminates the need for manual coding or full transcript review. Our system employs a novel multi-agent framework, where specialized LLM agents assume roles to enhance theme quality and alignment with human analysis. To further improve thematic relevance, we optionally integrate reinforcement learning from human feedback (RLHF). This supports scalable, patient-centered analysis of large qualitative datasets and allows LLMs to be fine-tuned for specific clinical contexts.</t>
+          <t xml:space="preserve">
+ The intelligent scheduling of autonomous trucks at intersections in open-pit coal mines poses a fundamental challenge due to nonlinear dynamics and complex multi-truck interactions under gradient–load coupling. Unlike existing intersection control studies that are mainly designed for flat urban roads and neglect mining-specific physical constraints, this study proposes a Gradient-Load Aware Multi-Agent Attention-Enhanced DDPG (GLA-MA-MADDPG) approach that explicitly embeds mining-domain physical laws into multi-agent reinforcement learning for intersection scheduling. A gradient–load dynamic coupling model is developed to inject physics fidelity into MARL-based intersection scheduling, capturing nonlinear and load-sensitive kinematics overlooked by flat-road assumptions in prior studies. To handle coordination under these constraints, we design a task-oriented multi-dimensional attention mechanism that jointly interprets physical heterogeneity, asymmetric dynamics, priorities, and collision risks. Additionally, a gradient-aware adaptive priority strategy redefines right-of-way as a physics-grounded, state-dependent process, ensuring safe and preferential passage for loaded and downhill trucks. In the simulated four-branch gradient intersection environment, the proposed GLA-MA-MADDPG method achieves substantial performance gains over traditional MADDPG across 20 independent runs. Specifically, it improves throughput by 23.5%, reduces average transit time by 8.3%, decreases waiting time by 31.2%, and lowers the collision rate from 3.47‰ to 1.32%, achieving efficiency gains of 39.2% in mixed uphill–downhill scenarios. Overall, this study contributes a first-of-its-kind integration of physics-informed gradient–load modeling with attention-driven MARL, providing a generalizable computational framework for intelligent intersection scheduling in open-pit mining and other large-scale, safety-critical engineering systems.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4235,21 +4188,21 @@
         <v>1</v>
       </c>
       <c r="L52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-DESPACHO-MINERO</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4258,27 +4211,27 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-DESPACHO-MINERO'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SMoA: Improving Multi-agent Large Language Models with Sparse Mixture-of-Agents</t>
+          <t>Gradientsys: A Multi-Agent LLM Scheduler with ReAct Orchestration</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dawei Li; Zhen Tan; Peijia Qian; Yifan Li; Kumar Satvik Chaudhary; Lijie Hu; Jiayi Shen</t>
+          <t>Xin-Yuan Song; Zeyu Wang; Siyi Wu; Tianyu Shi; Lynn Ai</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pacific-Asia Conference on Knowledge Discovery and Data Mining</t>
+          <t>arXiv.org</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4288,12 +4241,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10.48550/arXiv.2411.03284</t>
+          <t>10.48550/arXiv.2507.06520</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>While multi-agent systems have been shown to significantly enhance the performance of Large Language Models (LLMs) across various tasks and applications, the dense interaction between scaling agents potentially hampers their efficiency and diversity. To address these challenges, we draw inspiration from the sparse mixture-of-agents (SMoE) and propose a sparse mixture-of-agents (SMoA) framework to improve the efficiency and diversity of multi-agent LLMs. Unlike completely connected structures, SMoA introduces novel Response Selection and Early Stopping mechanisms to sparsify information flows among individual LLM agents, striking a balance between performance and efficiency. Additionally, inspired by the expert diversity principle in SMoE frameworks for workload balance between experts, we assign distinct role descriptions to each LLM agent, fostering diverse and divergent thinking. Extensive experiments on reasoning, alignment, and fairness benchmarks demonstrate that SMoA achieves performance comparable to traditional mixture-of-agents approaches but with significantly lower computational costs. Further analysis reveals that SMoA is more stable, has a greater capacity to scale, and offers considerable potential through hyper-parameter optimization. Code and data will be available at: https://github.com/David-Li0406/SMoA.</t>
+          <t>We present Gradientsys, a next-generation multi-agent scheduling framework that coordinates diverse specialized AI agents using a typed Model-Context Protocol (MCP) and a ReAct-based dynamic planning loop. At its core, Gradientsys employs an LLM-powered scheduler for intelligent one-to-many task dispatch, enabling parallel execution of heterogeneous agents such as PDF parsers, web search modules, GUI controllers, and web builders. The framework supports hybrid synchronous/asynchronous execution, respects agent capacity constraints, and incorporates a robust retry-and-replan mechanism to handle failures gracefully. To promote transparency and trust, Gradientsys includes an observability layer streaming real-time agent activity and intermediate reasoning via Server-Sent Events (SSE). We offer an architectural overview and evaluate Gradientsys against existing frameworks in terms of extensibility, scheduling topology, tool reusability, parallelism, and observability. Experiments on the GAIA general-assistant benchmark show that Gradientsys achieves higher task success rates with reduced latency and lower API costs compared to a MinionS-style baseline, demonstrating the strength of its LLM-driven multi-agent orchestration.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4311,17 +4264,17 @@
         <v>1</v>
       </c>
       <c r="L53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4334,27 +4287,27 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MASC: Large language model-based multi-agent scheduling chain for flexible job shop scheduling problem</t>
+          <t>QS-MADS: quorum sensing perturbation-driven adaptive multi-agent scheduling for distributed power grids</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zelong Wang; Chenhui Wan; Jie Liu; Xi Zhang; Haifeng Wang; You-Min Hu; Zhongxu Hu</t>
+          <t>Kun Zeng; Yi-Xiao Cao; Hui Sun</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Advanced Engineering Informatics</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4364,10 +4317,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10.1016/j.aei.2025.103527</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>10.1038/s41598-026-57593-0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>The rapid proliferation of distributed energy resources (DERs) in modern power grids introduces unprecedented complexity into real-time dispatch scheduling, demanding solutions that can operate under high uncertainty, partial observability, and volatile renewable generation. Existing multi-agent reinforcement learning (MARL) approaches for grid dispatch often suffer from weak inter-agent coordination, sample inefficiency, and fragility under measurement noise, largely because they rely on either independent exploration or expensive hidden-state exchange. We propose QS-MADS, a quorum-sensing-driven adaptive multi-agent scheduling framework that combines a topology-aware graph attention encoder with a lightweight scalar QS signal. During centralised training and optional online adaptation, each agent emits one 32-bit QS criticality signal; the trainer aggregates these scalars into a population consensus that governs a differentiable adaptive perturbation module used only for policy-gradient exploration. At deployment, the stochastic perturbation is removed and each deterministic actor executes from its local k-hop graph embedding, avoiding pairwise hidden-state communication. On IEEE 118-bus, RTS-96, and the CIGRE medium-voltage microgrid benchmarks, QS-MADS achieves up to 25% higher cumulative dispatch reward, reduces voltage violation events by 31%, and converges in up to 40% fewer training episodes relative to the strongest baseline, while maintaining millisecond-level inference latency and robust performance under measurement noise.</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -4386,18 +4343,18 @@
         <v>1</v>
       </c>
       <c r="M54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4406,27 +4363,27 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FAMASO: fog-adaptive multi-agent scheduling optimization</t>
+          <t>DARC-Sched: A Data-Aware Multi-Agent Large Language Model Framework for Scalable Software Vulnerability Detection and Repair with Optimized Code Data Scheduling</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ganesan Nagabushnam; K. Kim; Yundo Choi</t>
+          <t>Yan-Jing Xu; Min Qiu Trine; Huan-Yu Wu</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cluster Computing</t>
+          <t>Fundamental Scientific Reports in Multidisciplinary Areas</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4436,10 +4393,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10.1007/s10586-025-05588-3</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>10.66238/fsrma113</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Software vulnerability detection and automated repair have become critical for ensuring the security and reliability of large-scale software systems, particularly in modern development environments where massive code repositories and continuous integration pipelines significantly increase the complexity of vulnerability management. However, existing approaches based on Large Language Models (LLMs) often suffer from limited scalability and inefficient code retrieval when operating on large-scale code corpora, leading to degraded detection accuracy and high inference latency. To address these challenges, this paper proposes DARC-Sched (Data-Aware Reasoning and Collaborative Scheduling framework), a Data-Aware Multi-Agent Large Language Model framework that integrates multi-agent collaborative reasoning with optimized code data scheduling mechanisms for scalable vulnerability detection and repair. Specifically, DARC-Sched employs multiple specialized agents to perform vulnerability localization, evidence retrieval, verification, patch generation, and security validation, while a hierarchical data scheduling module dynamically prioritizes and caches vulnerability-relevant code segments based on learned risk-aware access patterns. Experimental results on benchmark datasets demonstrate that DARC-Sched achieves a 2.9% improvement in F1-score over strong retrieval-augmented baselines, reaching 91.9% F1-score, while reducing average retrieval latency by approximately 33% (from 295 ms to 198 ms). These results validate that integrating data-aware scheduling with multi-agent reasoning significantly improves both detection accuracy and system efficiency in large-scale software vulnerability analysis</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -4455,17 +4416,17 @@
         <v>1</v>
       </c>
       <c r="L55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4478,27 +4439,27 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Safe causal-graph primal-dual multi-agent scheduling for energy- and latency-constrained edge-assisted cognitive radio networks</t>
+          <t>MASC: Large language model-based multi-agent scheduling chain for flexible job shop scheduling problem</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T. Kannan; M. Lavanya; A. Ponraj; C. M. Nalayini</t>
+          <t>Zelong Wang; Chenhui Wan; Jie Liu; Xi Zhang; Haifeng Wang; You-Min Hu; Zhongxu Hu</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Advanced Engineering Informatics</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4508,14 +4469,10 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10.1038/s41598-026-60121-9</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Edge-assisted cognitive radio networks require efficient scheduling mechanisms to jointly manage opportunistic spectrum access, task offloading, energy consumption, and latency constraints. Existing multi-agent scheduling approaches often rely on fixed penalty terms or average queue-based constraints, which may not effectively control service-level violations under uncertain spectrum availability and dynamic edge-resource contention. This work proposes SCOPE, a Safe Causal-Graph Primal–Dual multi-agent scheduling framework for energy- and latency-constrained edge-assisted cognitive radio networks. The major strength of SCOPE is its integrated design, where belief-state augmentation improves decision-making under imperfect spectrum sensing, dual-relational causal graph coordination separately models’ interference coupling and computation-resource contention, and CVaR-based primal–dual optimization regulates tail-risk violations of latency and energy constraints. The framework follows a centralized-training and decentralized-execution structure, enabling coordinated learning during training while supporting scalable decentralized scheduling during deployment. Simulation results under dynamic user mobility, stochastic task arrivals, and varying primary-user activity show that SCOPE improves latency, energy efficiency, service-level constraint satisfaction, and throughput compared with existing scheduling methods. Ablation analysis further confirms the individual contribution of belief modeling, graph coordination, and risk-sensitive constraint enforcement.</t>
-        </is>
-      </c>
+          <t>10.1016/j.aei.2025.103527</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -4534,18 +4491,18 @@
         <v>1</v>
       </c>
       <c r="M56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4554,27 +4511,27 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ScheduleNet: Learn to solve multi-agent scheduling problems with reinforcement learning</t>
+          <t>A Large Language Model-based Multi-Agent Framework to Autonomously Design Algorithms for Earth Observation Satellite Scheduling Problem</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Junyoung Park; Sanjar Bakhtiyar; Jinkyoo Park</t>
+          <t>Jiawei Chen; Yingguo Chen; Duc Trong Pham; Yan-Jie Song; Jian Wu; Lining Xing; Ying-Wu Chen</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>arXiv.org</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4582,12 +4539,12 @@
           <t>journal</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>We propose ScheduleNet, a RL-based real-time scheduler, that can solve various types of multi-agent scheduling problems. We formulate these problems as a semi-MDP with episodic reward (makespan) and learn ScheduleNet, a decentralized decision-making policy that can effectively coordinate multiple agents to complete tasks. The decision making procedure of ScheduleNet includes: (1) representing the state of a scheduling problem with the agent-task graph, (2) extracting node embeddings for agent and tasks nodes, the important relational information among agents and tasks, by employing the type-aware graph attention (TGA), and (3) computing the assignment probability with the computed node embeddings. We validate the effectiveness of ScheduleNet as a general learning-based scheduler for solving various types of multi-agent scheduling tasks, including multiple salesman traveling problem (mTSP) and job shop scheduling problem (JSP).</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10.1016/j.eng.2025.10.027</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -4606,18 +4563,18 @@
         <v>1</v>
       </c>
       <c r="M57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4626,27 +4583,27 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>An Integrated Approach to Multi-Agent Scheduling with Bounded Objectives</t>
+          <t>Low Carbon Scheduling of Integrated Energy System Based on Large Language Model-Embedded Multi-Agent Reinforcement Learning</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fandel Lin; Han Zhang; T. K. S. Kumar; Craig A. Knoblock</t>
+          <t>Chen Xia; Tong Gou; Yinliang Xu; Ye Guo; Hongbin Sun</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SIGSPATIAL/GIS</t>
+          <t>IEEE Transactions on Smart Grid</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4656,12 +4613,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10.1145/3678717.3691224</t>
+          <t>10.1109/TSG.2026.3672814</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Road inspection and cleaning are crucial to securing driving safety. Deploying a fleet of robots that run through a city can inspect and clean pavements without causing road closure. To achieve high coverage, one has to prevent robots from going through a road segment more than once. However, robots may need more than one visit to a particular road segment to inspect a defect. The uncertain success rate of defect inspection and the unknown maximum number of defects hinder the efficacy. Such uncertainty and constraints in objectives can also be seen in security patrolling, trip planning, and network maintenance. We target the problem of multi-agent scheduling with bounded objectives. The scheduling aims for maximum road network coverage while ensuring sufficient visits to particular road segments for defect identification of an uncertain subject, such as potholes and faded markings during road inspection or crimes and parking violations during security patrolling. We leverage an approximate bi-objective algorithm and propose a hierarchical circular route-planning algorithm. Our approach maximizes the road coverage among robots and decreases the search space when maximizing defect identification. Evaluation on a real-world dataset shows that our approach achieves the Pareto optimal among comparative methods, outperforming existing methods by at least one optimization objective.</t>
+          <t>The complex multi-energy coupling characteristics inherent to integrated energy system (IES) present unprecedented challenges for the implementation of low-carbon scheduling. Existing optimization methods often exhibit limitations in system scalability, algorithm adaptivity, and carbon reduction efficacy for complex IES. This paper proposes a Large Language Model (LLM)-Embedded Multi-Agent Reinforcement Learning (LEMARL) to address the aforementioned issues. The proposed method integrates the global perception capability of LLMs with the dynamic optimization capability of MARL. Specifically, the LLM-Embedded module generates high-quality reward functions and policy frameworks from a global perspective, while the MARL module leverages these LLM-generated strategies for distributed interactive iterations—greatly enhancing computation efficiency and scalability. Simulation results demonstrate that LEMARL reduces carbon emissions by 7.76% and simultaneously decreases operating costs by 4.49% in a small-scale IES. Furthermore, LEMARL also exhibits superior applicability and scalability in large-scale IES of the IEEE 141-bus power grid integrated with 51-node thermal system.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4682,18 +4639,18 @@
         <v>1</v>
       </c>
       <c r="M58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4702,27 +4659,27 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WHALES: A Multi-Agent Scheduling Dataset for Enhanced Cooperation in Autonomous Driving</t>
+          <t>Large language model-empowered dynamic scheduling for intelligent hybrid flow shop using multi-agent deep reinforcement learning</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Yinsong Wang; Si-Wei Chen; Ziyi Song; Sheng Zhou</t>
+          <t>Wenbin Gu; Yushang Cao; Yu-Xin Li; Nuandong Li; Lei Wang; Na Tang; Minghai Yuan; Fengque Pei</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>IEEE/RJS International Conference on Intelligent RObots and Systems</t>
+          <t>Advanced Engineering Informatics</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4732,14 +4689,10 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>10.1109/IROS60139.2025.11247472</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Cooperative perception research is hindered by the limited availability of datasets that capture the complexity of real-world Vehicle-to-Everything (V2X) interactions, particularly under dynamic communication constraints. To address this gap, we introduce WHALES (Wireless enHanced Autonomous vehicles with Large number of Engaged agentS), the first large-scale V2X dataset explicitly designed to benchmark communication-aware agent scheduling and scalable cooperative perception. WHALES introduces a new benchmark that enables state-of-the-art (SOTA) research in communication-aware cooperative perception, featuring an average of 8.4 cooperative agents per scene and 2.01 million annotated 3D objects across diverse traffic scenarios. It incorporates detailed communication metadata to emulate real-world communication bottlenecks, enabling rigorous evaluation of scheduling strategies. To further advance the field, we propose the Coverage-Aware Historical Scheduler (CAHS), a novel scheduling baseline that selects agents based on historical viewpoint coverage, improving perception performance over existing SOTA methods. WHALES bridges the gap between simulated and real-world V2X challenges, providing a robust framework for exploring perception-scheduling co-design, cross-data generalization, and scalability limits. The WHALES dataset and code are available at https://github.com/chensiweiTHU/WHALES.</t>
-        </is>
-      </c>
+          <t>10.1016/j.aei.2025.104294</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -4758,18 +4711,18 @@
         <v>1</v>
       </c>
       <c r="M59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4778,27 +4731,27 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Multi-Agent Scheduling for Network Management</t>
+          <t>AI Metropolis: Scaling Large Language Model-based Multi-Agent Simulation with Out-of-order Execution</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Qin Shao; Yidan Zhang; Yue Wang; Sai Han; Lexi Xu; Zhao-Ning Wang; Xin-Zhou Cheng; Gang Zhu; Hao-Wen Sun; Xing-Jun Chi</t>
+          <t>Zhiqiang Xie; Hao Kang; Ying Sheng; Tushar Krishna; Kayvon Fatahalian; Christoforos E. Kozyrakis</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IEEE International Conference on High Performance Computing and Communications</t>
+          <t>arXiv.org</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4808,12 +4761,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10.1109/HPCC67675.2025.00190</t>
+          <t>10.48550/arXiv.2411.03519</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>With the rapid development in 6G networks, traditional network operation and maintenance (O&amp;M) approaches are insufficient to handle the scale and real-time demands. This paper presents a novel O&amp;M system, applying a multiagent scheduling algorithm to autonomously detect, diagnose, and resolve network faults. The system is structured in five layers: Data, Data Model, Agent, Application, and Interaction layers. And five classes of agents are integrated. Experimental results show the system's ability to outperform manual processes, which demonstrates the efficiency for the demanding needs of nextgeneration network management.</t>
+          <t>With more advanced natural language understanding and reasoning capabilities, large language model (LLM)-powered agents are increasingly developed in simulated environments to perform complex tasks, interact with other agents, and exhibit emergent behaviors relevant to social science and gaming. However, current multi-agent simulations frequently suffer from inefficiencies due to the limited parallelism caused by false dependencies, resulting in performance bottlenecks. In this paper, we introduce AI Metropolis, a simulation engine that improves the efficiency of LLM agent simulations by incorporating out-of-order execution scheduling. By dynamically tracking real dependencies between agents, AI Metropolis minimizes false dependencies, enhancing parallelism and enabling efficient hardware utilization. Our evaluations demonstrate that AI Metropolis achieves speedups from 1.3x to 4.15x over standard parallel simulation with global synchronization, approaching optimal performance as the number of agents increases.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4831,17 +4784,17 @@
         <v>1</v>
       </c>
       <c r="L60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4854,27 +4807,27 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>An Asynchronous Consensus Method With Low Communication Traffic and High Efficiency for Distributed Multi-Agent Scheduling</t>
+          <t>Modular Task Decomposition and Dynamic Collaboration in Multi-Agent Systems Driven by Large Language Models</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Runfeng Chen; Jie Li; Yiting Chen; Yuchong Huang; Xiangke Wang; Lin-Cheng Shen</t>
+          <t>Shuaidong Pan; Di Wu</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Mobile Computing</t>
+          <t>2025 6th International Conference on Information Science, Parallel and Distributed Systems (ISPDS)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4884,10 +4837,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>10.1109/TMC.2025.3591038</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>10.1109/ISPDS67367.2025.11390999</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>This paper addresses the limitations of a single agent in task decomposition and collaboration during complex task execution, and proposes a multi-agent architecture for modular task decomposition and dynamic collaboration based on large language models. The method first converts natural language task descriptions into unified semantic representations through a large language model. On this basis, a modular decomposition mechanism is introduced to break down the overall goal into multiple hierarchical sub-tasks. Then, dynamic scheduling and routing mechanisms enable reasonable division of labor and real-time collaboration among agents, allowing the system to adjust strategies continuously according to environmental feedback, thus maintaining efficiency and stability in complex tasks. Furthermore, a constraint parsing and global consistency mechanism is designed to ensure coherent connections between sub-tasks and balanced workload, preventing performance degradation caused by redundant communication or uneven resource allocation. The experiments validate the architecture across multiple dimensions, including task success rate, decomposition efficiency, sub-task coverage, and collaboration balance. The results show that the proposed method outperforms existing approaches in both overall performance and robustness, achieving a better balance between task complexity and communication overhead. In conclusion, this study demonstrates the effectiveness and feasibility of language-driven task decomposition and dynamic collaboration in multi-agent systems, providing a systematic solution for task execution in complex environments.</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -4906,18 +4863,18 @@
         <v>1</v>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4926,27 +4883,27 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Multi-agent Scheduling to Minimize Total Completion Times</t>
+          <t>Design and Teaching Practice of an Intelligent Learning Path Planning System Based on Large Language Models and Multi-Agent Collaboration</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rubing Chen; Yuan Gao; Jin-Jiang Yuan; Qiulan Zhao</t>
+          <t>Wei Liu; Fang Li; Lingling Tan; Yafan Chen; Lian-Peng Li</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Journal of the Operations Research Society of China</t>
+          <t>Higher Education and Practice</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4956,10 +4913,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10.1007/s40305-025-00598-9</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>10.62381/h261501</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>To improve personalized teaching quality and autonomous learning outcomes, and to address the common problems in traditional online education, including uniform learning paths, fragmented knowledge systems, and rapid forgetting after learning, this paper takes the design and implementation of an intelligent learning path planning system as a case of teaching reform. The system integrates large language models, knowledge graphs, and multi-agent technologies, and builds core functional modules for intelligent path generation, multi-channel retrieval enhancement, adaptive replanning, and review scheduling. The system supports a shift in teaching practice from a course-centered model to a learner-centered model. The teaching practice results show that the proposed system, which is based on advanced artificial intelligence technologies, effectively reduces students’ cognitive load, stimulates their interest in autonomous learning, and improves the teaching effectiveness and adaptive intervention capability of intelligent education systems.</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -4975,17 +4936,17 @@
         <v>1</v>
       </c>
       <c r="L62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -4998,19 +4959,19 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Multi-agent Scheduling for Shared Manufacturing Systems</t>
+          <t>Large Language Model-based Test Case Generation for GP Agents</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ege Duran; Cemalettin Ozturk; Barry O'Sullivan</t>
+          <t>Steven Jorgensen; Giorgia Nadizar; Gloria Pietropolli; Luca Manzoni; Eric Medvet; U. O’Reilly; Erik Hemberg</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5018,7 +4979,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>IEEE International Symposium on Multimedia</t>
+          <t>Annual Conference on Genetic and Evolutionary Computation</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5028,10 +4989,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10.1016/j.procs.2025.01.134</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>10.1145/3638529.3654056</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Genetic programming (GP) is a popular problem-solving and optimization technique. However, generating effective test cases for training and evaluating GP programs requires strong domain knowledge. Furthermore, GP programs often prematurely converge on local optima when given excessively difficult problems early in their training. Curriculum learning (CL) has been effective in addressing similar issues across different reinforcement learning (RL) domains, but it requires the manual generation of progressively difficult test cases as well as their careful scheduling. In this work, we leverage the domain knowledge and the strong generative abilities of large language models (LLMs) to generate effective test cases of increasing difficulties and schedule them according to various curricula. We show that by integrating a curriculum scheduler with LLM-generated test cases we can effectively train a GP agent player with environments-based curricula for a single-player game and opponent-based curricula for a multi-player game. Finally, we discuss the benefits and challenges of implementing this method for other problem domains.</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -5047,17 +5012,17 @@
         <v>1</v>
       </c>
       <c r="L63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5070,27 +5035,27 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NLNS-MASPF for solving Multi-Agent scheduling and Path-Finding</t>
+          <t>MedScrubCrew: A Medical Multi-Agent Framework for Automating Appointment Scheduling Based on Patient-Provider Profile Resource Matching</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Heemang Park; Kyuree Ahn; Jinkyoo Park</t>
+          <t>Jose M. Ruiz Mejia; Danda B. Rawat</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>IEEE/RJS International Conference on Intelligent RObots and Systems</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5100,12 +5065,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10.1109/IROS58592.2024.10802133</t>
+          <t>10.3390/healthcare13141649</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>In this work, we propose a novel method, NLNS-MASPF, to solve the Multi-Agent Scheduling and Pathfinding (MASPF) problem. The problem exhibits a bi-level structure, consisting of High-level Scheduling and Low-level Pathfinding. Our method applies a graph neural network in the high-level scheduling process and utilizes a MAPF solver with a schedule segmenting technique in the low-level pathfinding process. Through these approaches, NLNS-MASPF has experimentally demonstrated superior performance compared to the previous state-of-the-art MASPF algorithm, LNS-PBS, in solving the MASPF problem.</t>
+          <t>Background: With advancements in Generative Artificial Intelligence, various industries have made substantial efforts to integrate this technology to enhance the efficiency and effectiveness of existing processes or identify potential weaknesses. Context, however, remains a crucial factor in leveraging intelligence, especially in high-stakes sectors such as healthcare, where contextual understanding can lead to life-changing outcomes. Objective: This research aims to develop a practical medical multi-agent system framework capable of automating appointment scheduling and triage classification, thus improving operational efficiency in healthcare settings. Methods: We present MedScrubCrew, a multi-agent framework integrating established technologies: Gale-Shapley stable matching algorithm for optimal patient-provider allocation, knowledge graphs for semantic compatibility profiling, and specialized large language model-based agents. The framework is designed to emulate the collaborative decision making processes typical of medical teams. Results: Our evaluation demonstrates that combining these components within a cohesive multi-agent architecture substantially enhances operational efficiency, task completeness, and contextual relevance in healthcare scheduling workflows. Conclusions: MedScrubCrew provides a practical, implementable blueprint for healthcare automation, addressing significant inefficiencies in real-world appointment scheduling and patient triage scenarios.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5146,27 +5111,27 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>H-MAS: Hierarchical Multi-Agent Scheduling for Multi-Tenant LLM Serving</t>
+          <t>On the Prospects of Incorporating Large Language Models (LLMs) in Automated Planning and Scheduling (APS)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yuhan Liu; Cong Xu; Qi Jia; Yi-Hua Wang; Fei-Yu Chen; Liang Jin; Lu Liu; Yaqian Zhao; Yuting Ding; Xiang Li</t>
+          <t>Vishal Pallagani; Kaushik Roy; Bharath Muppasani; F. Fabiano; A. Loreggia; K. Murugesan; Biplav Srivastava; F. Rossi; L. Horesh; Amit P. Sheth</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Annual Meeting of the Association for Computational Linguistics</t>
+          <t>International Conference on Automated Planning and Scheduling</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5176,10 +5141,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.18653/v1/2026.findings-acl.1946</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>10.1609/icaps.v34i1.31503</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Automated Planning and Scheduling is among the growing areas in Artificial Intelligence (AI) where mention of LLMs has gained popularity. Based on a comprehensive review of 126 papers, this paper investigates eight categories based on the unique applications of LLMs in addressing various aspects of planning problems: language translation, plan generation, model construction, multi-agent planning, interactive planning, heuristics optimization, tool integration, and brain-inspired planning. For each category, we articulate the issues considered and existing gaps. A critical insight resulting from our review is that the true potential of LLMs unfolds when they are integrated with traditional symbolic planners, pointing towards a promising neuro-symbolic approach. This approach effectively combines the generative aspects of LLMs with the precision of classical planning methods. By synthesizing insights from existing literature, we underline the potential of this integration to address complex planning challenges. Our goal is to encourage the ICAPS community to recognize the complementary strengths of LLMs and symbolic planners, advocating for a direction in automated planning that leverages these synergistic capabilities to develop more advanced and intelligent planning systems. We aim to keep the categorization of papers updated on https://ai4society.github.io/LLM-Planning-Viz/, a collaborative resource that allows researchers to contribute and add new literature to the categorization.</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>semantic_scholar</t>
@@ -5218,27 +5187,27 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Multi-agent scheduling algorithm</t>
+          <t>Applying Large Language Models as Hybrid-Algorithm Experts for Job Shop Scheduling Problems*</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>O. R. Norkin; A. S. Miroshnichenko; S. S. Parfenova</t>
+          <t>Zhiyan Zhang; Zimo Ji; Haixuan Wang; Jun-Kai Wang</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Informatization and communication</t>
+          <t>IEEE International Conference on Systems, Man and Cybernetics</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5248,12 +5217,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10.34219/2078-8320-2023-14-2-49-53</t>
+          <t>10.1109/SMC58881.2025.11342734</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>This paper is devoted to one of the problems of making an optimal schedule, namely, the problem of forming a schedule of classes. Planning activities of any scale requires the creation of a schedule, the following of which, ideally, should bring benefits and the maximum possible benefit both to the common cause and to everyone individually. As a result, people have a need to create an optimal schedule that will con-sider all the limitations and requirements of its users and at the same time solve the tasks in the most profitable way. To date, there are various methods, approaches and algorithms for scheduling, each of which has its own advantages and disadvantages. This paper discusses the main existing approaches to solving the scheduling problem, shows the advantage of a multi-agent approach, proposes the organization of a multi-agent system, strategies for multi-agent interaction and a multi-agent scheduling algorithm.</t>
+          <t>Efficient production scheduling of aviation components is essential for optimizing manufacturing equipment and resource utilization. Traditional scheduling requires experts to develop complex models and optimization algorithms, making the process time-consuming and expertise-dependent. This paper proposes LLM-Scheduling, a multi-agent framework where each agent, powered by a large language model (LLM), autonomously executes scheduling tasks based on natural language inputs. The framework integrates retrieval-augmented generation (RAG) to provide relevant domain knowledge and employs a Hybrid-Search strategy to enhance optimization performance. Experimental results demonstrate that LLM-Scheduling outperforms conventional approaches in most cases, achieving more efficient scheduling and improved adaptability in dynamic manufacturing environments. Moreover, the framework shows promise in enhancing energy efficiency by optimizing machine utilization and reducing idle time. These findings suggest that LLM-driven scheduling can significantly contribute to smarter and more sustainable manufacturing processes.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5274,18 +5243,18 @@
         <v>1</v>
       </c>
       <c r="M66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -5294,27 +5263,27 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2023; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MASS: Multi-Agent Scheduling System for Intelligent Surveillance</t>
+          <t>A survey on large language models for scheduling: From problem modeling to optimization algorithm generation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dong-Ki Noh; Jun-Ho Choi; Jeongsik Choi; Dasol Byun; Youngjae Kim; Hyoung-Rock Kim; Seungmin Baek; Seunghwan Lee; H. Myung</t>
+          <t>Xiang W.</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2022 19th International Conference on Ubiquitous Robots (UR)</t>
+          <t>Advanced Engineering Informatics</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5324,17 +5293,13 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10.1109/ur55393.2022.9826281</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>With the recent development of autonomous driving technology, attempts to apply autonomous mobile robots to security and surveillance have been continued. Algorithms such as localization, obstacle avoidance, and path planning are essential for indoor autonomous driving of mobile robots. Among them, in this study, we deal with the path planning algorithm of mobile robots. In particular, the goal is to generate a path that covers the entire area of the given map, focusing on patrolling and guarding. We propose an algorithm that divides the generated path into multiple paths and allocates it to multi-robots by clustering. In addition, we propose a path planning algorithm that considers weights assigned on the probability map. We evaluated the performance of robot path generation with a real-world map from a testbed at the Korea Institute of Robotics and Technology Convergence (KIRO) in Pohang, Korea. This study also presents the results of cases with and without importance weights.</t>
-        </is>
-      </c>
+          <t>10.1016/j.aei.2026.104946</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -5350,18 +5315,18 @@
         <v>1</v>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5370,27 +5335,27 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2022; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MedScrubCrew: A Medical Multi-Agent Framework for Automating Appointment Scheduling Based on Patient-Provider Profile Resource Matching</t>
+          <t>LLM-assisted quality-aware GA–multi-agent deep deterministic policy gradient framework for multi-robot collaborative scheduling in construction quality control</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jose M. Ruiz Mejia; Danda B. Rawat</t>
+          <t>Zhu M.</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automation in Construction</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5400,17 +5365,13 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10.3390/healthcare13141649</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Background: With advancements in Generative Artificial Intelligence, various industries have made substantial efforts to integrate this technology to enhance the efficiency and effectiveness of existing processes or identify potential weaknesses. Context, however, remains a crucial factor in leveraging intelligence, especially in high-stakes sectors such as healthcare, where contextual understanding can lead to life-changing outcomes. Objective: This research aims to develop a practical medical multi-agent system framework capable of automating appointment scheduling and triage classification, thus improving operational efficiency in healthcare settings. Methods: We present MedScrubCrew, a multi-agent framework integrating established technologies: Gale-Shapley stable matching algorithm for optimal patient-provider allocation, knowledge graphs for semantic compatibility profiling, and specialized large language model-based agents. The framework is designed to emulate the collaborative decision making processes typical of medical teams. Results: Our evaluation demonstrates that combining these components within a cohesive multi-agent architecture substantially enhances operational efficiency, task completeness, and contextual relevance in healthcare scheduling workflows. Conclusions: MedScrubCrew provides a practical, implementable blueprint for healthcare automation, addressing significant inefficiencies in real-world appointment scheduling and patient triage scenarios.</t>
-        </is>
-      </c>
+          <t>10.1016/j.autcon.2026.107203</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5426,18 +5387,18 @@
         <v>1</v>
       </c>
       <c r="M68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>MAS-LLM</t>
+          <t>MAS-SCHEDULING</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -5446,27 +5407,27 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CurriculumPT: LLM-Based Multi-Agent Autonomous Penetration Testing with Curriculum-Guided Task Scheduling</t>
+          <t>Text-to-control of networked microgrids: A large language model agent workflow for reinforcement learning scheduling</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Xing-Yu Wu; Yunzhe Tian; Yuanwan Chen; Ping Ye; Xiaoshu Cui; Jingqi Jia; Shouyang Li; Jiqiang Liu; Wen-Jia Niu</t>
+          <t>Liu C.</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Applied Sciences</t>
+          <t>Applied Energy</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5476,17 +5437,13 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10.3390/app15169096</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>While autonomous driving systems and intelligent transportation infrastructures become increasingly software-defined and network-connected, ensuring their cybersecurity has become a critical component of traffic safety. Large language models (LLMs) have recently shown promise in automating aspects of penetration testing, yet most existing approaches remain limited to simple, single-step exploits. They struggle to handle complex, multi-stage vulnerabilities that demand precise coordination, contextual reasoning, and knowledge reuse. This is particularly problematic in safety-critical domains, such as autonomous vehicles, where subtle software flaws can cascade across interdependent subsystems. In this work, we present CurriculumPT, a novel LLM-based penetration testing framework specifically designed for the security of intelligent systems. CurriculumPT combines curriculum learning and a multi-agent system to enable LLM agents to progressively acquire and apply exploitation skills across common vulnerabilities and exposures-based tasks. Through a structured progression from simple to complex vulnerabilities, agents build and refine an experience knowledge base that supports generalization to new attack surfaces without requiring model fine-tuning. We evaluate CurriculumPT on 15 real-world vulnerabilities scenarios and demonstrate that it outperforms three state-of-the-art baselines by up to 18 percentage points in exploit success rate, while achieving superior efficiency in execution time and resource usage. Our results confirm that CurriculumPT is capable of autonomous, scalable penetration testing and knowledge transfer, laying the groundwork for intelligent security auditing of modern autonomous driving systems and other cyberphysical transportation platforms.</t>
-        </is>
-      </c>
+          <t>10.1016/j.apenergy.2026.128289</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5522,27 +5479,27 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Research on collaborative scheduling strategies of multi-agent agricultural machinery groups</t>
+          <t>MARS: Multi-Agent Rescheduling Framework with Large Language Models for Human-Centric Manufacturing</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ziyi Wang; Fan Zhang; Shijing Ma; Hailong Wang; Shunyao Zhang; Xiao-Zhong Gao</t>
+          <t>Park J.</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Journal of Manufacturing Systems</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5552,17 +5509,13 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10.1038/s41598-025-93848-y</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Addressing the challenges of high scheduling costs and low efficiency in the collaborative operations of agricultural machinery across multiple dispatch centers, this paper develops a scheduling model designed to minimize total costs. It introduces a Multi-Center and Multi-Machine Path Planning Algorithm Based on Deep Reinforcement Learning (MCMPP-DRL). Firstly, a deep reinforcement learning environment is established, and a policy network utilizing the attention mechanism is designed. Subsequently, the network model is trained to improve its solution capabilities using the policy gradient algorithm (REINFORCE). Finally, the solution is optimized through a local search strategy. In this study, three dispatch centers were selected within the maize growing area of Hebei Province, and comparative analyses were conducted for 20, 40, 50, 100 and 120 farmlands, respectively.The results indicate that the MCMPP-DRL algorithm achieves a reduction in total scheduling costs of at least 9.66%, 14.34% and 24.41% compared to Ant Colony Optimization (ACO), Simulated Annealing (SA) and Genetic Algorithms(GA), respectively.The significant optimization in scheduling costs demonstrates that the MCMPP-DRL algorithm establishes a robust theoretical foundation and offers technical support for addressing complex scheduling problems involving multiple dispatch centers and multiple.</t>
-        </is>
-      </c>
+          <t>10.1016/j.jmsy.2026.07.015</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5578,18 +5531,18 @@
         <v>1</v>
       </c>
       <c r="M70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5598,27 +5551,27 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Multi-agent large language models as evolutionary optimizers for scheduling optimization</t>
+          <t>FedDualFix: Hierarchical federated learning for adaptive multi-agent program repair via dual-modality modeling</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Yidan Wang; Jia-Yin Wang; Zhiwei Chu</t>
+          <t>Ju X.</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Computers &amp; industrial engineering</t>
+          <t>Applied Soft Computing</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5628,13 +5581,13 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>10.1016/j.cie.2025.111197</t>
+          <t>10.1016/j.asoc.2026.115898</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5647,17 +5600,17 @@
         <v>1</v>
       </c>
       <c r="L71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5670,27 +5623,27 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Manufacturing resource-based self-organizing scheduling using multi-agent system and deep reinforcement learning</t>
+          <t>Tool-augmented LLM planning and decoupled scheduling for heterogeneous multi-agent lunar missions: A three-layer architecture</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Yuxin Li; Qi-Hao Liu; Xin-Yu Li; Liang Gao</t>
+          <t>E J.</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Journal of manufacturing systems</t>
+          <t>Robotics and Autonomous Systems</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5700,13 +5653,13 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10.1016/j.jmsy.2025.01.004</t>
+          <t>10.1016/j.robot.2026.105581</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5742,19 +5695,19 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Learning distributed tracking protocol for LPV multi-agent systems from noisy data</t>
+          <t>Latency-Constrained Dependency-Aware Heterogeneous Multimodal LLM Agents Placement at Edge</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chen W.</t>
+          <t>Zhang B.</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -5762,7 +5715,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Applied Mathematics and Computation</t>
+          <t>IEEE Internet of Things Journal</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5772,7 +5725,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10.1016/j.amc.2026.130233</t>
+          <t>10.1109/JIOT.2026.3695932</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -5821,12 +5774,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A dynamic scheduling framework for co-working space resources optimized by multi-agent reinforcement learning</t>
+          <t>Simulation Method for Multi-crew Construction Processes Based on Large Language Model-powered Agent</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ding S.</t>
+          <t>Yifan W.</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -5834,7 +5787,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Discover Artificial Intelligence</t>
+          <t>Xitong Fangzhen Xuebao Journal of System Simulation</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5844,7 +5797,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>10.1007/s44163-026-00873-5</t>
+          <t>10.16182/j.issn1004731x.joss.25-0990</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -5866,18 +5819,18 @@
         <v>1</v>
       </c>
       <c r="M74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="b">
         <v>0</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5886,19 +5839,19 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Multi-agent deep reinforcement learning for joint user scheduling and power allocation in the GEO-LEO co-existing satellite system</t>
+          <t>Hybrid task planning and scheduling in heterogeneous multi-agent systems based on LLMs and constraint programming</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fan S.</t>
+          <t>Palmieri J.</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -5906,7 +5859,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Acta Astronautica</t>
+          <t>Robotics and Autonomous Systems</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5916,7 +5869,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10.1016/j.actaastro.2026.07.014</t>
+          <t>10.1016/j.robot.2026.105480</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -5965,12 +5918,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Physics-informed multi-agent deep reinforcement learning for dynamic emergency resource scheduling in marine oil spills</t>
+          <t>Multi-Agent Social Simulation: Protocolizing LLM-Driven Agent-Based Modeling as a Quantitative Research Method †</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Yang J.</t>
+          <t>Hu X.</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5978,7 +5931,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Transportation Research Part E Logistics and Transportation Review</t>
+          <t>AI Switzerland</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5988,7 +5941,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10.1016/j.tre.2026.105148</t>
+          <t>10.3390/ai7080279</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -6007,17 +5960,17 @@
         <v>1</v>
       </c>
       <c r="L76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6030,19 +5983,19 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QS-MADS: quorum sensing perturbation-driven adaptive multi-agent scheduling for distributed power grids</t>
+          <t>JW-ASTClaw: A Generalizable Multi-agent Framework for Autonomous Solar Telescope and Its Implementation within Chinese Meridian Project</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zeng K.</t>
+          <t>Tong L.Y.</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6050,7 +6003,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Research in Astronomy and Astrophysics</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6060,7 +6013,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10.1038/s41598-026-57593-0</t>
+          <t>10.1088/1674-4527/ae8b87</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -6079,7 +6032,7 @@
         <v>1</v>
       </c>
       <c r="L77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6093,7 +6046,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6109,12 +6062,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>InGS-MAQ: Innovative guided search optimized multi-agent-based scheme for priority scheduling and channel estimation for eavesdropping suppression in wireless networks</t>
+          <t>Priority-Driven Hierarchical Multi-Agent Systems with Fine-Tuned LLMs</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Najan A.S.</t>
+          <t>Tudela A.</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6122,7 +6075,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Computers and Security</t>
+          <t>Applied Sciences Switzerland</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6132,7 +6085,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10.1016/j.cose.2026.105078</t>
+          <t>10.3390/app16168250</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -6181,12 +6134,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Multi-agent collaborative reinforcement learning for dynamic flexible job shop scheduling under machine random failures</t>
+          <t>OptiSMR: A unified framework for structured reasoning and self-repairing multi-agent system optimized for generalization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wu H.</t>
+          <t>Chen J.</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6194,7 +6147,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Computers and Operations Research</t>
+          <t>Knowledge Based Systems</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6204,7 +6157,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10.1016/j.cor.2026.107644</t>
+          <t>10.1016/j.knosys.2026.116143</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -6223,7 +6176,7 @@
         <v>1</v>
       </c>
       <c r="L79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6237,7 +6190,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -6253,36 +6206,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A multi-agent reinforcement learning scheduling algorithm integrating state graph and task graph structural modeling for ride-sharing dispatching</t>
+          <t>Towards a Natural Language Interface for Flexible Multi-Agent Task Assignment</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sha J.</t>
+          <t>Brawer, Jake; Bishop, Kayleigh; Hayes, Bradley; Roncone, Alessandro</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-026-35004-8</t>
-        </is>
-      </c>
+          <t>PROCEEDINGS OF THE 2023 AAAI FALL SYMPOSIA, VOL 2 NO 1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6298,18 +6243,18 @@
         <v>1</v>
       </c>
       <c r="M80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -6318,43 +6263,35 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-LLM'; year=2023; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Degradation-constrained multi-agent reinforcement learning with centralized training and decentralized execution for vehicle-to-grid optimization in renewable-dominated distribution networks</t>
+          <t>On the Prospects of Incorporating Large Language Models (LLMs) in Automated Planning and Scheduling (APS)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shiferaw Y.</t>
+          <t>Pallagani, Vishal; Muppasani, Bharath Chandra; Roy, Kaushik; Fabiano, Francesco; Loreggia, Andrea; Murugesan, Keerthiram; Srivastava, Biplav; Rossi, Francesca; Horesh, Lior; Sheth, Amit</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-026-55471-3</t>
-        </is>
-      </c>
+          <t>PROCEEDINGS OF THE THIRTY-FOURTH INTERNATIONAL CONFERENCE ON AUTOMATED PLANNING AND SCHEDULING, VOL 34</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>wos</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6367,21 +6304,21 @@
         <v>1</v>
       </c>
       <c r="L81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -6390,33 +6327,37 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2026; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>An Approach to Intelligent Control Public Transportation System Using a Multi-agent System</t>
+          <t>AutoTQA: Towards Autonomous Tabular Question Answering through Multi-Agent Large Language Models</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Morri, Nabil; Hadouaj, Sameh; Ben Said, Lamjed</t>
+          <t>Zhu, Jun-Peng; Cai, Peng; Xu, Kai; Li, Li; Sun, Yishen; Zhou, Shuai; Su, Haihuang; Tang, Liu; Liu, Qi</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lecture Notes in Business Information Processing</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>PROCEEDINGS OF THE VLDB ENDOWMENT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-75418-1_12</t>
+          <t>10.14778/3685800.3685816</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -6438,18 +6379,18 @@
         <v>0</v>
       </c>
       <c r="M82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -6458,33 +6399,37 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2024; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Event-Triggered Control for Linear Multi-agent Systems Under DoS Attacks</t>
+          <t>A Dual-Agent Collaboration Framework Based on LLMs for Nursing Robots to Perform Bimanual Coordination Tasks</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sun, Lianghui; Lyu, Jianting; Gao, Dai; Wang, Xin</t>
+          <t>Zhao, Zhendong; Yue, Xiaotian; Xie, Jiexin; Fang, Chuanhong; Shao, Zhenzhou; Guo, Shijie</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lecture Notes in Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>IEEE ROBOTICS AND AUTOMATION LETTERS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10.1007/978-981-15-8458-9_35</t>
+          <t>10.1109/LRA.2025.3533476</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -6526,31 +6471,39 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Computation and Communication Co-Design for Real-Time Monitoring and Control in Multi-Agent Systems</t>
+          <t>AutoHMA-LLM: Efficient Task Coordination and Execution in Heterogeneous Multi-Agent Systems Using Hybrid Large Language Models</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tripathi, Vishrant; Ballotta, Luca; Carlone, Luca; Modiano, Eytan</t>
+          <t>Yang, Tingting; Feng, Ping; Guo, Qixin; Zhang, Jindi; Zhang, Xiufeng; Ning, Jiahong; Wang, Xinghan; Mao, Zhongyang</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2021 19TH INTERNATIONAL SYMPOSIUM ON MODELING AND OPTIMIZATION IN MOBILE, AD HOC, AND WIRELESS NETWORKS (WIOPT)</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+          <t>IEEE TRANSACTIONS ON COGNITIVE COMMUNICATIONS AND NETWORKING</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>10.1109/TCCN.2025.3528892</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
@@ -6567,21 +6520,21 @@
         <v>1</v>
       </c>
       <c r="L84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -6590,31 +6543,39 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Improving Multi-agent Coordination by Learning to Estimate Contention</t>
+          <t>EV Charging System Considering Power Dispatching Based on Multi-Agent LLMs and CGAN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Danassis, Panayiotis; Wiedemair, Florian; Faltings, Boi</t>
+          <t>Niu, Zeyuan; Li, Jiamei; Ai, Qian; Jiang, Jiamei; Yang, Qiunan; Zhou, Haojie</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PROCEEDINGS OF THE THIRTIETH INTERNATIONAL JOINT CONFERENCE ON ARTIFICIAL INTELLIGENCE, IJCAI 2021</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+          <t>IEEE TRANSACTIONS ON INTELLIGENT TRANSPORTATION SYSTEMS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>10.1109/TITS.2025.3564389</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
@@ -6631,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="L85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -6645,7 +6606,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -6654,33 +6615,37 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>An Adaptive Charging Scheduling for Electric Vehicles Using Multiagent Reinforcement Learning</t>
+          <t>OC-HMAS: Dynamic Self-Organization and Self-Correction in Heterogeneous Multiagent Systems Using Multimodal Large Models</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lee, Xian-Long; Yang, Hong-Tzer; Tang, Wenjun; Toosi, Adel N.; Lam, Edward</t>
+          <t>Feng, Ping; Yang, Tingting; Liang, Mingyang; Wang, Lin; Gao, Yuan</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lecture Notes in Computer Science</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>IEEE INTERNET OF THINGS JOURNAL</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-91431-8_17</t>
+          <t>10.1109/JIOT.2025.3545496</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -6699,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="L86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -6713,7 +6678,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6722,31 +6687,39 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Distributed Fair Scheduling for Information Exchange in Multi-Agent Systems</t>
+          <t>Multi-agent large language models as evolutionary optimizers for scheduling optimization</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Raeis, Majid; Golestani, S. Jamaloddin</t>
+          <t>Wang, Yidan; Wang, Jiayin; Chu, Zhiwei</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PROCEEDINGS OF THE THIRTY-FIRST INTERNATIONAL CONFERENCE ON AUTOMATED PLANNING AND SCHEDULING, VOL 31</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+          <t>COMPUTERS &amp; INDUSTRIAL ENGINEERING</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>10.1016/j.cie.2025.111197</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
@@ -6766,18 +6739,18 @@
         <v>1</v>
       </c>
       <c r="M87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6786,27 +6759,27 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Simultaneous Production and AGV Scheduling using Multi-Agent Deep Reinforcement Learning</t>
+          <t>Enhancing LLM QoS Through Cloud-Edge Collaboration: A Diffusion-Based Multi-Agent Reinforcement Learning Approach</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Popper, Jens; Yfantis, Vassilios; Ruskowski, Martin</t>
+          <t>Yao, Zhi; Tang, Zhiqing; Yang, Wenmian; Jia, Weijia</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Procedia CIRP</t>
+          <t>IEEE TRANSACTIONS ON SERVICES COMPUTING</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6816,7 +6789,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>10.1016/j.procir.2021.11.257</t>
+          <t>10.1109/TSC.2025.3562362</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -6835,7 +6808,7 @@
         <v>1</v>
       </c>
       <c r="L88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -6849,7 +6822,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6858,31 +6831,39 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>An Optimal scheduling method using multi-agent A* for Autonomous shuttle bus</t>
+          <t>Large language model-driven multi-agent systems for improving production efficiency and reducing carbon emissions in manufacturing</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Peng, Jiali; Wei Shangguan; Lu Zhang; Yue Cao</t>
+          <t>Wu, Tao; Li, Jie; Bao, Jinsong; Liu, Qiang</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2021 PROCEEDINGS OF THE 40TH CHINESE CONTROL CONFERENCE (CCC)</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+          <t>COMPUTERS &amp; INDUSTRIAL ENGINEERING</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10.1016/j.cie.2025.111299</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
@@ -6899,17 +6880,17 @@
         <v>1</v>
       </c>
       <c r="L89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -6922,27 +6903,27 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type=None; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Resource Allocation and Service Provisioning in Multi-Agent Cloud Robotics: A Comprehensive Survey</t>
+          <t>AnnCoder: A Mti-Agent-Based Code Generation and Optimization Model</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Afrin, Mahbuba; Jin, Jiong; Rahman, Akhlaqur; Rahman, Ashfaqur; Wan, Jiafu; Hossain, Ekram</t>
+          <t>Zhang, Zhenhua; Wang, Jianfeng; Li, Zhengyang; Wang, Yunpeng; Zheng, Jiayun</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>IEEE COMMUNICATIONS SURVEYS AND TUTORIALS</t>
+          <t>SYMMETRY-BASEL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6952,7 +6933,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10.1109/COMST.2021.3061435</t>
+          <t>10.3390/sym17071087</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -6971,17 +6952,17 @@
         <v>1</v>
       </c>
       <c r="L90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>MAS-SCHEDULING</t>
+          <t>MAS-LLM</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -6994,151 +6975,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Multi-Agent Reinforcement Learning-Based Resource Management for End-to-End Network Slicing</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Kim, Yohan; Lim, Hyuk</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>IEEE ACCESS</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>10.1109/ACCESS.2021.3072435</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>wos</t>
-        </is>
-      </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="b">
-        <v>0</v>
-      </c>
-      <c r="K91" t="b">
-        <v>1</v>
-      </c>
-      <c r="L91" t="b">
-        <v>0</v>
-      </c>
-      <c r="M91" t="b">
-        <v>0</v>
-      </c>
-      <c r="N91" t="b">
-        <v>0</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>MAS-SCHEDULING</t>
-        </is>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>An Improved Acceleration Method Based on Multi-Agent System for AGVs Conflict-Free Path Planning in Automated Terminals</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Guo, Kunlun; Zhu, Jin; Shen, Lei</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>IEEE ACCESS</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>10.1109/ACCESS.2020.3047916</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>wos</t>
-        </is>
-      </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92" t="b">
-        <v>1</v>
-      </c>
-      <c r="L92" t="b">
-        <v>0</v>
-      </c>
-      <c r="M92" t="b">
-        <v>0</v>
-      </c>
-      <c r="N92" t="b">
-        <v>0</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>MAS-SCHEDULING</t>
-        </is>
-      </c>
-      <c r="P92" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-SCHEDULING'; year=2021; incluido: no se activaron criterios de exclusión o pendiente</t>
+          <t>preprint=no; antiguedad=dentro del limite o sin año; mas=true; venue_type='journal'; categoria='MAS-LLM'; year=2025; incluido: no se activaron criterios de exclusión o pendiente</t>
         </is>
       </c>
     </row>
